--- a/artfynd/A 29779-2025 artfynd.xlsx
+++ b/artfynd/A 29779-2025 artfynd.xlsx
@@ -2819,7 +2819,7 @@
         <v>126017342</v>
       </c>
       <c r="B21" t="n">
-        <v>97216</v>
+        <v>97218</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>126017344</v>
       </c>
       <c r="B22" t="n">
-        <v>92510</v>
+        <v>92518</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 29779-2025 artfynd.xlsx
+++ b/artfynd/A 29779-2025 artfynd.xlsx
@@ -2819,7 +2819,7 @@
         <v>126017342</v>
       </c>
       <c r="B21" t="n">
-        <v>97218</v>
+        <v>97222</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>126017344</v>
       </c>
       <c r="B22" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 29779-2025 artfynd.xlsx
+++ b/artfynd/A 29779-2025 artfynd.xlsx
@@ -2819,7 +2819,7 @@
         <v>126017342</v>
       </c>
       <c r="B21" t="n">
-        <v>97222</v>
+        <v>97223</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 29779-2025 artfynd.xlsx
+++ b/artfynd/A 29779-2025 artfynd.xlsx
@@ -2819,7 +2819,7 @@
         <v>126017342</v>
       </c>
       <c r="B21" t="n">
-        <v>97223</v>
+        <v>97225</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>126017344</v>
       </c>
       <c r="B22" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 29779-2025 artfynd.xlsx
+++ b/artfynd/A 29779-2025 artfynd.xlsx
@@ -2819,7 +2819,7 @@
         <v>126017342</v>
       </c>
       <c r="B21" t="n">
-        <v>97225</v>
+        <v>97227</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>126017344</v>
       </c>
       <c r="B22" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 29779-2025 artfynd.xlsx
+++ b/artfynd/A 29779-2025 artfynd.xlsx
@@ -2819,7 +2819,7 @@
         <v>126017342</v>
       </c>
       <c r="B21" t="n">
-        <v>97227</v>
+        <v>97229</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>126017344</v>
       </c>
       <c r="B22" t="n">
-        <v>92526</v>
+        <v>92528</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 29779-2025 artfynd.xlsx
+++ b/artfynd/A 29779-2025 artfynd.xlsx
@@ -2819,7 +2819,7 @@
         <v>126017342</v>
       </c>
       <c r="B21" t="n">
-        <v>97229</v>
+        <v>97233</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>126017344</v>
       </c>
       <c r="B22" t="n">
-        <v>92528</v>
+        <v>92532</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 29779-2025 artfynd.xlsx
+++ b/artfynd/A 29779-2025 artfynd.xlsx
@@ -2819,7 +2819,7 @@
         <v>126017342</v>
       </c>
       <c r="B21" t="n">
-        <v>97233</v>
+        <v>97236</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 29779-2025 artfynd.xlsx
+++ b/artfynd/A 29779-2025 artfynd.xlsx
@@ -2819,7 +2819,7 @@
         <v>126017342</v>
       </c>
       <c r="B21" t="n">
-        <v>97236</v>
+        <v>97245</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>126017344</v>
       </c>
       <c r="B22" t="n">
-        <v>92532</v>
+        <v>92535</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 29779-2025 artfynd.xlsx
+++ b/artfynd/A 29779-2025 artfynd.xlsx
@@ -3028,10 +3028,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126600545</v>
+        <v>126600584</v>
       </c>
       <c r="B23" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3063,10 +3063,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>406516</v>
+        <v>406438</v>
       </c>
       <c r="R23" t="n">
-        <v>6856086</v>
+        <v>6855633</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3125,10 +3125,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126600584</v>
+        <v>126600666</v>
       </c>
       <c r="B24" t="n">
-        <v>79598</v>
+        <v>79011</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3136,21 +3136,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3160,10 +3160,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>406438</v>
+        <v>406495</v>
       </c>
       <c r="R24" t="n">
-        <v>6855633</v>
+        <v>6856163</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3222,10 +3222,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126600668</v>
+        <v>126600545</v>
       </c>
       <c r="B25" t="n">
-        <v>78980</v>
+        <v>79629</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3233,21 +3233,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3257,10 +3257,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>406439</v>
+        <v>406516</v>
       </c>
       <c r="R25" t="n">
-        <v>6855714</v>
+        <v>6856086</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3319,10 +3319,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126600627</v>
+        <v>126600688</v>
       </c>
       <c r="B26" t="n">
-        <v>78739</v>
+        <v>78417</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3330,21 +3330,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3354,10 +3354,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>406497</v>
+        <v>406442</v>
       </c>
       <c r="R26" t="n">
-        <v>6855840</v>
+        <v>6855707</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3416,10 +3416,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126600666</v>
+        <v>126600668</v>
       </c>
       <c r="B27" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3451,10 +3451,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>406495</v>
+        <v>406439</v>
       </c>
       <c r="R27" t="n">
-        <v>6856163</v>
+        <v>6855714</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3614,10 +3614,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126600623</v>
+        <v>126600621</v>
       </c>
       <c r="B29" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3649,10 +3649,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>406420</v>
+        <v>406382</v>
       </c>
       <c r="R29" t="n">
-        <v>6856050</v>
+        <v>6856055</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3711,10 +3711,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126600621</v>
+        <v>126600627</v>
       </c>
       <c r="B30" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3746,10 +3746,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>406382</v>
+        <v>406497</v>
       </c>
       <c r="R30" t="n">
-        <v>6856055</v>
+        <v>6855840</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3808,10 +3808,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126600688</v>
+        <v>126600623</v>
       </c>
       <c r="B31" t="n">
-        <v>78386</v>
+        <v>78770</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3819,21 +3819,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3843,10 +3843,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>406442</v>
+        <v>406420</v>
       </c>
       <c r="R31" t="n">
-        <v>6855707</v>
+        <v>6856050</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3905,32 +3905,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126600635</v>
+        <v>126600608</v>
       </c>
       <c r="B32" t="n">
-        <v>78738</v>
+        <v>97320</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>221941</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3940,10 +3940,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>406535</v>
+        <v>406378</v>
       </c>
       <c r="R32" t="n">
-        <v>6855969</v>
+        <v>6856046</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4002,32 +4002,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126600608</v>
+        <v>126600620</v>
       </c>
       <c r="B33" t="n">
-        <v>97245</v>
+        <v>78770</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221941</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4037,10 +4037,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>406378</v>
+        <v>406376</v>
       </c>
       <c r="R33" t="n">
-        <v>6856046</v>
+        <v>6856016</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4102,7 +4102,7 @@
         <v>126600639</v>
       </c>
       <c r="B34" t="n">
-        <v>78738</v>
+        <v>78769</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4196,10 +4196,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126600679</v>
+        <v>126600635</v>
       </c>
       <c r="B35" t="n">
-        <v>78647</v>
+        <v>78769</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4207,21 +4207,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4231,10 +4231,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>406407</v>
+        <v>406535</v>
       </c>
       <c r="R35" t="n">
-        <v>6856127</v>
+        <v>6855969</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4293,10 +4293,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126600620</v>
+        <v>126600556</v>
       </c>
       <c r="B36" t="n">
-        <v>78739</v>
+        <v>79629</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4304,21 +4304,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4328,10 +4328,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>406376</v>
+        <v>406389</v>
       </c>
       <c r="R36" t="n">
-        <v>6856016</v>
+        <v>6856021</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4390,10 +4390,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126600556</v>
+        <v>126600679</v>
       </c>
       <c r="B37" t="n">
-        <v>79598</v>
+        <v>78678</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4401,21 +4401,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>406389</v>
+        <v>406407</v>
       </c>
       <c r="R37" t="n">
-        <v>6856021</v>
+        <v>6856127</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4490,7 +4490,7 @@
         <v>126600677</v>
       </c>
       <c r="B38" t="n">
-        <v>92535</v>
+        <v>92609</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         <v>126600561</v>
       </c>
       <c r="B39" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4684,7 +4684,7 @@
         <v>126600579</v>
       </c>
       <c r="B40" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>126600553</v>
       </c>
       <c r="B41" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4875,10 +4875,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126600626</v>
+        <v>126600567</v>
       </c>
       <c r="B42" t="n">
-        <v>78739</v>
+        <v>79629</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4886,21 +4886,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4910,10 +4910,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>406473</v>
+        <v>406471</v>
       </c>
       <c r="R42" t="n">
-        <v>6855839</v>
+        <v>6855896</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4972,10 +4972,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126600567</v>
+        <v>126600626</v>
       </c>
       <c r="B43" t="n">
-        <v>79598</v>
+        <v>78770</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4983,21 +4983,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5007,10 +5007,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>406471</v>
+        <v>406473</v>
       </c>
       <c r="R43" t="n">
-        <v>6855896</v>
+        <v>6855839</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5072,7 +5072,7 @@
         <v>126600629</v>
       </c>
       <c r="B44" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5166,10 +5166,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126600572</v>
+        <v>126600656</v>
       </c>
       <c r="B45" t="n">
-        <v>79598</v>
+        <v>79011</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5177,21 +5177,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5201,10 +5201,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>406428</v>
+        <v>406626</v>
       </c>
       <c r="R45" t="n">
-        <v>6855941</v>
+        <v>6856024</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5263,10 +5263,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126600576</v>
+        <v>126600548</v>
       </c>
       <c r="B46" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5298,10 +5298,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>406439</v>
+        <v>406278</v>
       </c>
       <c r="R46" t="n">
-        <v>6855706</v>
+        <v>6855989</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5360,10 +5360,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126600619</v>
+        <v>126600559</v>
       </c>
       <c r="B47" t="n">
-        <v>78739</v>
+        <v>79629</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5371,21 +5371,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5395,10 +5395,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>406365</v>
+        <v>406397</v>
       </c>
       <c r="R47" t="n">
-        <v>6856013</v>
+        <v>6856067</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5457,10 +5457,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126600559</v>
+        <v>126600582</v>
       </c>
       <c r="B48" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5492,10 +5492,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>406397</v>
+        <v>406432</v>
       </c>
       <c r="R48" t="n">
-        <v>6856067</v>
+        <v>6855636</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5554,10 +5554,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126600548</v>
+        <v>126600572</v>
       </c>
       <c r="B49" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5589,10 +5589,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>406278</v>
+        <v>406428</v>
       </c>
       <c r="R49" t="n">
-        <v>6855989</v>
+        <v>6855941</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5651,10 +5651,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126600656</v>
+        <v>126600576</v>
       </c>
       <c r="B50" t="n">
-        <v>78980</v>
+        <v>79629</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5662,21 +5662,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5686,10 +5686,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>406626</v>
+        <v>406439</v>
       </c>
       <c r="R50" t="n">
-        <v>6856024</v>
+        <v>6855706</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5748,10 +5748,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126600582</v>
+        <v>126600619</v>
       </c>
       <c r="B51" t="n">
-        <v>79598</v>
+        <v>78770</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5759,21 +5759,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5783,10 +5783,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>406432</v>
+        <v>406365</v>
       </c>
       <c r="R51" t="n">
-        <v>6855636</v>
+        <v>6856013</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5848,7 +5848,7 @@
         <v>126600554</v>
       </c>
       <c r="B52" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5942,10 +5942,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126600586</v>
+        <v>126600558</v>
       </c>
       <c r="B53" t="n">
-        <v>91167</v>
+        <v>79629</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5953,21 +5953,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3242</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5977,10 +5977,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>406331</v>
+        <v>406382</v>
       </c>
       <c r="R53" t="n">
-        <v>6855997</v>
+        <v>6856055</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6039,10 +6039,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126600618</v>
+        <v>126600643</v>
       </c>
       <c r="B54" t="n">
-        <v>78739</v>
+        <v>78769</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6050,21 +6050,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6074,10 +6074,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>406323</v>
+        <v>406462</v>
       </c>
       <c r="R54" t="n">
-        <v>6856001</v>
+        <v>6855914</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6136,10 +6136,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126600643</v>
+        <v>126600618</v>
       </c>
       <c r="B55" t="n">
-        <v>78738</v>
+        <v>78770</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6147,21 +6147,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6171,10 +6171,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>406462</v>
+        <v>406323</v>
       </c>
       <c r="R55" t="n">
-        <v>6855914</v>
+        <v>6856001</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6233,10 +6233,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126600558</v>
+        <v>126600586</v>
       </c>
       <c r="B56" t="n">
-        <v>79598</v>
+        <v>91241</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6244,21 +6244,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>3242</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6268,10 +6268,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>406382</v>
+        <v>406331</v>
       </c>
       <c r="R56" t="n">
-        <v>6856055</v>
+        <v>6855997</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6333,7 +6333,7 @@
         <v>126600663</v>
       </c>
       <c r="B57" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6427,32 +6427,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126600601</v>
+        <v>126600645</v>
       </c>
       <c r="B58" t="n">
-        <v>98382</v>
+        <v>78769</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221952</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6462,10 +6462,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>406524</v>
+        <v>406440</v>
       </c>
       <c r="R58" t="n">
-        <v>6856188</v>
+        <v>6855714</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6524,32 +6524,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126600590</v>
+        <v>126600601</v>
       </c>
       <c r="B59" t="n">
-        <v>79569</v>
+        <v>98457</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>229821</v>
+        <v>221952</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6559,10 +6559,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>406293</v>
+        <v>406524</v>
       </c>
       <c r="R59" t="n">
-        <v>6855983</v>
+        <v>6856188</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6621,10 +6621,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126600645</v>
+        <v>126600590</v>
       </c>
       <c r="B60" t="n">
-        <v>78738</v>
+        <v>79600</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6632,21 +6632,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6656,10 +6656,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>406440</v>
+        <v>406293</v>
       </c>
       <c r="R60" t="n">
-        <v>6855714</v>
+        <v>6855983</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6718,10 +6718,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126600654</v>
+        <v>126600653</v>
       </c>
       <c r="B61" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6753,10 +6753,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>406623</v>
+        <v>406536</v>
       </c>
       <c r="R61" t="n">
-        <v>6855990</v>
+        <v>6855607</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6815,10 +6815,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126600565</v>
+        <v>126600636</v>
       </c>
       <c r="B62" t="n">
-        <v>79598</v>
+        <v>78769</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6826,21 +6826,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6850,10 +6850,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>406485</v>
+        <v>406307</v>
       </c>
       <c r="R62" t="n">
-        <v>6855873</v>
+        <v>6855949</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6912,10 +6912,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126600653</v>
+        <v>126600565</v>
       </c>
       <c r="B63" t="n">
-        <v>78980</v>
+        <v>79629</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6923,21 +6923,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6947,10 +6947,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>406536</v>
+        <v>406485</v>
       </c>
       <c r="R63" t="n">
-        <v>6855607</v>
+        <v>6855873</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7009,10 +7009,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126600636</v>
+        <v>126600684</v>
       </c>
       <c r="B64" t="n">
-        <v>78738</v>
+        <v>78417</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7020,21 +7020,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7044,10 +7044,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>406307</v>
+        <v>406294</v>
       </c>
       <c r="R64" t="n">
-        <v>6855949</v>
+        <v>6855983</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7106,10 +7106,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126600614</v>
+        <v>126600654</v>
       </c>
       <c r="B65" t="n">
-        <v>78739</v>
+        <v>79011</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7117,21 +7117,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7141,10 +7141,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>406294</v>
+        <v>406623</v>
       </c>
       <c r="R65" t="n">
-        <v>6856039</v>
+        <v>6855990</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7203,10 +7203,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126600684</v>
+        <v>126600614</v>
       </c>
       <c r="B66" t="n">
-        <v>78386</v>
+        <v>78770</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7214,21 +7214,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7241,7 +7241,7 @@
         <v>406294</v>
       </c>
       <c r="R66" t="n">
-        <v>6855983</v>
+        <v>6856039</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7300,10 +7300,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126600613</v>
+        <v>126600644</v>
       </c>
       <c r="B67" t="n">
-        <v>78739</v>
+        <v>78769</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7311,21 +7311,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7335,10 +7335,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>406469</v>
+        <v>406406</v>
       </c>
       <c r="R67" t="n">
-        <v>6855892</v>
+        <v>6855855</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7371,11 +7371,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-07-11</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>På stubbe med 3 brandljud</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7402,10 +7397,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126600624</v>
+        <v>126600664</v>
       </c>
       <c r="B68" t="n">
-        <v>78739</v>
+        <v>79011</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7413,21 +7408,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7437,10 +7432,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>406429</v>
+        <v>406512</v>
       </c>
       <c r="R68" t="n">
-        <v>6856032</v>
+        <v>6856169</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7499,10 +7494,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126600644</v>
+        <v>126600683</v>
       </c>
       <c r="B69" t="n">
-        <v>78738</v>
+        <v>78417</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7510,21 +7505,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7534,10 +7529,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>406406</v>
+        <v>406500</v>
       </c>
       <c r="R69" t="n">
-        <v>6855855</v>
+        <v>6856028</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7596,10 +7591,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126600664</v>
+        <v>126600624</v>
       </c>
       <c r="B70" t="n">
-        <v>78980</v>
+        <v>78770</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7607,21 +7602,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7631,10 +7626,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>406512</v>
+        <v>406429</v>
       </c>
       <c r="R70" t="n">
-        <v>6856169</v>
+        <v>6856032</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7693,10 +7688,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126600683</v>
+        <v>126600613</v>
       </c>
       <c r="B71" t="n">
-        <v>78386</v>
+        <v>78770</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7704,21 +7699,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7728,10 +7723,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>406500</v>
+        <v>406469</v>
       </c>
       <c r="R71" t="n">
-        <v>6856028</v>
+        <v>6855892</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7764,6 +7759,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>På stubbe med 3 brandljud</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7790,10 +7790,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126600640</v>
+        <v>126600551</v>
       </c>
       <c r="B72" t="n">
-        <v>78738</v>
+        <v>79629</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7801,21 +7801,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7825,10 +7825,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>406428</v>
+        <v>406323</v>
       </c>
       <c r="R72" t="n">
-        <v>6856010</v>
+        <v>6856001</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7887,10 +7887,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126600537</v>
+        <v>126600555</v>
       </c>
       <c r="B73" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7922,10 +7922,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>406520</v>
+        <v>406391</v>
       </c>
       <c r="R73" t="n">
-        <v>6855700</v>
+        <v>6856010</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7984,10 +7984,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126600552</v>
+        <v>126600569</v>
       </c>
       <c r="B74" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8019,10 +8019,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>406366</v>
+        <v>406463</v>
       </c>
       <c r="R74" t="n">
-        <v>6856013</v>
+        <v>6855915</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8081,10 +8081,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126600631</v>
+        <v>126600640</v>
       </c>
       <c r="B75" t="n">
-        <v>80955</v>
+        <v>78769</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8092,21 +8092,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1049</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8116,10 +8116,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>406419</v>
+        <v>406428</v>
       </c>
       <c r="R75" t="n">
-        <v>6855945</v>
+        <v>6856010</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8178,10 +8178,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126600555</v>
+        <v>126600552</v>
       </c>
       <c r="B76" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8213,10 +8213,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>406391</v>
+        <v>406366</v>
       </c>
       <c r="R76" t="n">
-        <v>6856010</v>
+        <v>6856013</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8275,10 +8275,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126600569</v>
+        <v>126600537</v>
       </c>
       <c r="B77" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8310,10 +8310,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>406463</v>
+        <v>406520</v>
       </c>
       <c r="R77" t="n">
-        <v>6855915</v>
+        <v>6855700</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8372,10 +8372,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126600551</v>
+        <v>126600631</v>
       </c>
       <c r="B78" t="n">
-        <v>79598</v>
+        <v>80986</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8383,21 +8383,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8407,10 +8407,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>406323</v>
+        <v>406419</v>
       </c>
       <c r="R78" t="n">
-        <v>6856001</v>
+        <v>6855945</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8469,10 +8469,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126600680</v>
+        <v>126600581</v>
       </c>
       <c r="B79" t="n">
-        <v>78647</v>
+        <v>79629</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8480,21 +8480,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8504,10 +8504,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>406390</v>
+        <v>406418</v>
       </c>
       <c r="R79" t="n">
-        <v>6856010</v>
+        <v>6855644</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8566,10 +8566,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126600615</v>
+        <v>126600571</v>
       </c>
       <c r="B80" t="n">
-        <v>78739</v>
+        <v>79629</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8577,21 +8577,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8601,10 +8601,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>406271</v>
+        <v>406431</v>
       </c>
       <c r="R80" t="n">
-        <v>6856003</v>
+        <v>6855941</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8663,10 +8663,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126600581</v>
+        <v>126600680</v>
       </c>
       <c r="B81" t="n">
-        <v>79598</v>
+        <v>78678</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8674,21 +8674,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8698,10 +8698,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>406418</v>
+        <v>406390</v>
       </c>
       <c r="R81" t="n">
-        <v>6855644</v>
+        <v>6856010</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8760,10 +8760,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126600571</v>
+        <v>126600615</v>
       </c>
       <c r="B82" t="n">
-        <v>79598</v>
+        <v>78770</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8771,21 +8771,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8795,10 +8795,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>406431</v>
+        <v>406271</v>
       </c>
       <c r="R82" t="n">
-        <v>6855941</v>
+        <v>6856003</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8857,10 +8857,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126600544</v>
+        <v>126600652</v>
       </c>
       <c r="B83" t="n">
-        <v>79598</v>
+        <v>79011</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8868,21 +8868,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8892,10 +8892,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>406538</v>
+        <v>406459</v>
       </c>
       <c r="R83" t="n">
-        <v>6855980</v>
+        <v>6855873</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8928,6 +8928,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>På gammeltall utan hänsynsmarkering</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8954,10 +8959,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126600560</v>
+        <v>126600544</v>
       </c>
       <c r="B84" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8989,10 +8994,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>406434</v>
+        <v>406538</v>
       </c>
       <c r="R84" t="n">
-        <v>6856017</v>
+        <v>6855980</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9051,10 +9056,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126600678</v>
+        <v>126600560</v>
       </c>
       <c r="B85" t="n">
-        <v>78647</v>
+        <v>79629</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9062,21 +9067,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9086,10 +9091,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>406585</v>
+        <v>406434</v>
       </c>
       <c r="R85" t="n">
-        <v>6856016</v>
+        <v>6856017</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9151,7 +9156,7 @@
         <v>126600546</v>
       </c>
       <c r="B86" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9245,10 +9250,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126600652</v>
+        <v>126600678</v>
       </c>
       <c r="B87" t="n">
-        <v>78980</v>
+        <v>78678</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9256,21 +9261,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9280,10 +9285,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>406459</v>
+        <v>406585</v>
       </c>
       <c r="R87" t="n">
-        <v>6855873</v>
+        <v>6856016</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9316,11 +9321,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-07-11</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>På gammeltall utan hänsynsmarkering</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9347,10 +9347,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126600657</v>
+        <v>126600577</v>
       </c>
       <c r="B88" t="n">
-        <v>78980</v>
+        <v>79629</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9358,21 +9358,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9382,10 +9382,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>406513</v>
+        <v>406461</v>
       </c>
       <c r="R88" t="n">
-        <v>6856139</v>
+        <v>6855692</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9444,32 +9444,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126600628</v>
+        <v>126600591</v>
       </c>
       <c r="B89" t="n">
-        <v>78739</v>
+        <v>91284</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>228912</v>
+        <v>5447</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9479,10 +9479,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>406471</v>
+        <v>406266</v>
       </c>
       <c r="R89" t="n">
-        <v>6855896</v>
+        <v>6856149</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9541,10 +9541,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126600611</v>
+        <v>126600660</v>
       </c>
       <c r="B90" t="n">
-        <v>92727</v>
+        <v>79011</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9552,21 +9552,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9576,10 +9576,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>406433</v>
+        <v>406521</v>
       </c>
       <c r="R90" t="n">
-        <v>6855894</v>
+        <v>6856195</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9638,32 +9638,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126600591</v>
+        <v>126600657</v>
       </c>
       <c r="B91" t="n">
-        <v>91210</v>
+        <v>79011</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9673,10 +9673,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>406266</v>
+        <v>406513</v>
       </c>
       <c r="R91" t="n">
-        <v>6856149</v>
+        <v>6856139</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9735,10 +9735,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126600660</v>
+        <v>126600543</v>
       </c>
       <c r="B92" t="n">
-        <v>78980</v>
+        <v>79629</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9746,21 +9746,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9770,10 +9770,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>406521</v>
+        <v>406586</v>
       </c>
       <c r="R92" t="n">
-        <v>6856195</v>
+        <v>6856018</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9832,10 +9832,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126600630</v>
+        <v>126600611</v>
       </c>
       <c r="B93" t="n">
-        <v>78739</v>
+        <v>92802</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9843,21 +9843,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9867,10 +9867,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>406428</v>
+        <v>406433</v>
       </c>
       <c r="R93" t="n">
-        <v>6855941</v>
+        <v>6855894</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9929,10 +9929,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126600577</v>
+        <v>126600628</v>
       </c>
       <c r="B94" t="n">
-        <v>79598</v>
+        <v>78770</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9940,21 +9940,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9964,10 +9964,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>406461</v>
+        <v>406471</v>
       </c>
       <c r="R94" t="n">
-        <v>6855692</v>
+        <v>6855896</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10026,10 +10026,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126600543</v>
+        <v>126600630</v>
       </c>
       <c r="B95" t="n">
-        <v>79598</v>
+        <v>78770</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10037,21 +10037,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10061,10 +10061,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>406586</v>
+        <v>406428</v>
       </c>
       <c r="R95" t="n">
-        <v>6856018</v>
+        <v>6855941</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10123,10 +10123,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126600616</v>
+        <v>126600541</v>
       </c>
       <c r="B96" t="n">
-        <v>78739</v>
+        <v>79629</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10134,21 +10134,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10158,10 +10158,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>406293</v>
+        <v>406596</v>
       </c>
       <c r="R96" t="n">
-        <v>6855983</v>
+        <v>6855897</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10220,10 +10220,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126600575</v>
+        <v>126600585</v>
       </c>
       <c r="B97" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10255,10 +10255,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>406441</v>
+        <v>406436</v>
       </c>
       <c r="R97" t="n">
-        <v>6855713</v>
+        <v>6855599</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10317,10 +10317,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126600589</v>
+        <v>126600575</v>
       </c>
       <c r="B98" t="n">
-        <v>79569</v>
+        <v>79629</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10328,21 +10328,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10352,10 +10352,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>406271</v>
+        <v>406441</v>
       </c>
       <c r="R98" t="n">
-        <v>6856003</v>
+        <v>6855713</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10414,10 +10414,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126600541</v>
+        <v>126600563</v>
       </c>
       <c r="B99" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10449,10 +10449,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>406596</v>
+        <v>406460</v>
       </c>
       <c r="R99" t="n">
-        <v>6855897</v>
+        <v>6855846</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10511,10 +10511,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126600563</v>
+        <v>126600580</v>
       </c>
       <c r="B100" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10546,10 +10546,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>406460</v>
+        <v>406422</v>
       </c>
       <c r="R100" t="n">
-        <v>6855846</v>
+        <v>6855652</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10608,10 +10608,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126600585</v>
+        <v>126600681</v>
       </c>
       <c r="B101" t="n">
-        <v>79598</v>
+        <v>78678</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10619,21 +10619,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10643,10 +10643,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>406436</v>
+        <v>406422</v>
       </c>
       <c r="R101" t="n">
-        <v>6855599</v>
+        <v>6856055</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10705,10 +10705,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126600681</v>
+        <v>126600616</v>
       </c>
       <c r="B102" t="n">
-        <v>78647</v>
+        <v>78770</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10716,21 +10716,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10740,10 +10740,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>406422</v>
+        <v>406293</v>
       </c>
       <c r="R102" t="n">
-        <v>6856055</v>
+        <v>6855983</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10802,10 +10802,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126600580</v>
+        <v>126600589</v>
       </c>
       <c r="B103" t="n">
-        <v>79598</v>
+        <v>79600</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10813,21 +10813,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10837,10 +10837,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>406422</v>
+        <v>406271</v>
       </c>
       <c r="R103" t="n">
-        <v>6855652</v>
+        <v>6856003</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10899,10 +10899,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126600637</v>
+        <v>126600622</v>
       </c>
       <c r="B104" t="n">
-        <v>78738</v>
+        <v>78770</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10910,21 +10910,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10934,10 +10934,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>406389</v>
+        <v>406388</v>
       </c>
       <c r="R104" t="n">
-        <v>6856020</v>
+        <v>6856064</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10996,10 +10996,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126600622</v>
+        <v>126600637</v>
       </c>
       <c r="B105" t="n">
-        <v>78739</v>
+        <v>78769</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11007,21 +11007,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11031,10 +11031,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>406388</v>
+        <v>406389</v>
       </c>
       <c r="R105" t="n">
-        <v>6856064</v>
+        <v>6856020</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11096,7 +11096,7 @@
         <v>126600574</v>
       </c>
       <c r="B106" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11193,7 +11193,7 @@
         <v>126600655</v>
       </c>
       <c r="B107" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11287,10 +11287,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126600557</v>
+        <v>126600587</v>
       </c>
       <c r="B108" t="n">
-        <v>79598</v>
+        <v>75135</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11298,21 +11298,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11322,10 +11322,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>406381</v>
+        <v>406631</v>
       </c>
       <c r="R108" t="n">
-        <v>6856048</v>
+        <v>6855979</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11384,10 +11384,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126600587</v>
+        <v>126600557</v>
       </c>
       <c r="B109" t="n">
-        <v>75075</v>
+        <v>79629</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11395,21 +11395,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11419,10 +11419,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>406631</v>
+        <v>406381</v>
       </c>
       <c r="R109" t="n">
-        <v>6855979</v>
+        <v>6856048</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11481,32 +11481,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126600651</v>
+        <v>126600606</v>
       </c>
       <c r="B110" t="n">
-        <v>91263</v>
+        <v>97314</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11516,10 +11516,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>406515</v>
+        <v>406618</v>
       </c>
       <c r="R110" t="n">
-        <v>6856173</v>
+        <v>6856011</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11578,10 +11578,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126600570</v>
+        <v>126600573</v>
       </c>
       <c r="B111" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11613,10 +11613,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>406442</v>
+        <v>406409</v>
       </c>
       <c r="R111" t="n">
-        <v>6855938</v>
+        <v>6855915</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11675,10 +11675,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126600650</v>
+        <v>126600570</v>
       </c>
       <c r="B112" t="n">
-        <v>91263</v>
+        <v>79629</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11686,21 +11686,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11710,10 +11710,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>406523</v>
+        <v>406442</v>
       </c>
       <c r="R112" t="n">
-        <v>6856161</v>
+        <v>6855938</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11772,10 +11772,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126600617</v>
+        <v>126600651</v>
       </c>
       <c r="B113" t="n">
-        <v>78739</v>
+        <v>91337</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11783,21 +11783,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>228912</v>
+        <v>5432</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11807,10 +11807,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>406303</v>
+        <v>406515</v>
       </c>
       <c r="R113" t="n">
-        <v>6855965</v>
+        <v>6856173</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11869,32 +11869,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126600606</v>
+        <v>126600650</v>
       </c>
       <c r="B114" t="n">
-        <v>97239</v>
+        <v>91337</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11904,10 +11904,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>406618</v>
+        <v>406523</v>
       </c>
       <c r="R114" t="n">
-        <v>6856011</v>
+        <v>6856161</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11966,10 +11966,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126600573</v>
+        <v>126600542</v>
       </c>
       <c r="B115" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12001,10 +12001,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>406409</v>
+        <v>406587</v>
       </c>
       <c r="R115" t="n">
-        <v>6855915</v>
+        <v>6855895</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12170,10 +12170,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126600542</v>
+        <v>126600617</v>
       </c>
       <c r="B117" t="n">
-        <v>79598</v>
+        <v>78770</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12181,21 +12181,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12205,10 +12205,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>406587</v>
+        <v>406303</v>
       </c>
       <c r="R117" t="n">
-        <v>6855895</v>
+        <v>6855965</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12270,7 +12270,7 @@
         <v>126600658</v>
       </c>
       <c r="B118" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12367,7 +12367,7 @@
         <v>126600549</v>
       </c>
       <c r="B119" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12464,7 +12464,7 @@
         <v>126600673</v>
       </c>
       <c r="B120" t="n">
-        <v>92535</v>
+        <v>92609</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12558,10 +12558,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126600682</v>
+        <v>126600642</v>
       </c>
       <c r="B121" t="n">
-        <v>78647</v>
+        <v>78769</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12569,21 +12569,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12593,10 +12593,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>406425</v>
+        <v>406485</v>
       </c>
       <c r="R121" t="n">
-        <v>6855965</v>
+        <v>6855875</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12655,10 +12655,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126600642</v>
+        <v>126600632</v>
       </c>
       <c r="B122" t="n">
-        <v>78738</v>
+        <v>78769</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12690,10 +12690,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>406485</v>
+        <v>406502</v>
       </c>
       <c r="R122" t="n">
-        <v>6855875</v>
+        <v>6855622</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12755,7 +12755,7 @@
         <v>126600535</v>
       </c>
       <c r="B123" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12849,32 +12849,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126600675</v>
+        <v>126600665</v>
       </c>
       <c r="B124" t="n">
-        <v>92535</v>
+        <v>79011</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12884,10 +12884,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>406442</v>
+        <v>406499</v>
       </c>
       <c r="R124" t="n">
-        <v>6855951</v>
+        <v>6856166</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12946,10 +12946,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126600562</v>
+        <v>126600634</v>
       </c>
       <c r="B125" t="n">
-        <v>79598</v>
+        <v>78769</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12957,21 +12957,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12981,10 +12981,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>406422</v>
+        <v>406580</v>
       </c>
       <c r="R125" t="n">
-        <v>6855969</v>
+        <v>6855911</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13043,10 +13043,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126600665</v>
+        <v>126600562</v>
       </c>
       <c r="B126" t="n">
-        <v>78980</v>
+        <v>79629</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13054,21 +13054,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13078,10 +13078,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>406499</v>
+        <v>406422</v>
       </c>
       <c r="R126" t="n">
-        <v>6856166</v>
+        <v>6855969</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13140,10 +13140,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126600634</v>
+        <v>126600682</v>
       </c>
       <c r="B127" t="n">
-        <v>78738</v>
+        <v>78678</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13151,21 +13151,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13175,10 +13175,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>406580</v>
+        <v>406425</v>
       </c>
       <c r="R127" t="n">
-        <v>6855911</v>
+        <v>6855965</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13237,32 +13237,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126600632</v>
+        <v>126600675</v>
       </c>
       <c r="B128" t="n">
-        <v>78738</v>
+        <v>92609</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13272,10 +13272,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>406502</v>
+        <v>406442</v>
       </c>
       <c r="R128" t="n">
-        <v>6855622</v>
+        <v>6855951</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13337,7 +13337,7 @@
         <v>126600672</v>
       </c>
       <c r="B129" t="n">
-        <v>92535</v>
+        <v>92609</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13434,7 +13434,7 @@
         <v>126600568</v>
       </c>
       <c r="B130" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13528,10 +13528,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126600625</v>
+        <v>126600538</v>
       </c>
       <c r="B131" t="n">
-        <v>78739</v>
+        <v>79629</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13539,21 +13539,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13563,10 +13563,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>406434</v>
+        <v>406578</v>
       </c>
       <c r="R131" t="n">
-        <v>6856017</v>
+        <v>6855748</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13625,10 +13625,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126600538</v>
+        <v>126600625</v>
       </c>
       <c r="B132" t="n">
-        <v>79598</v>
+        <v>78770</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13636,21 +13636,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13660,10 +13660,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>406578</v>
+        <v>406434</v>
       </c>
       <c r="R132" t="n">
-        <v>6855748</v>
+        <v>6856017</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13725,7 +13725,7 @@
         <v>126600638</v>
       </c>
       <c r="B133" t="n">
-        <v>78738</v>
+        <v>78769</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13822,7 +13822,7 @@
         <v>126600566</v>
       </c>
       <c r="B134" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13916,32 +13916,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126600676</v>
+        <v>126600536</v>
       </c>
       <c r="B135" t="n">
-        <v>92535</v>
+        <v>79629</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -13951,10 +13951,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>406414</v>
+        <v>406521</v>
       </c>
       <c r="R135" t="n">
-        <v>6855915</v>
+        <v>6855634</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14013,32 +14013,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126600594</v>
+        <v>126600676</v>
       </c>
       <c r="B136" t="n">
-        <v>57817</v>
+        <v>92609</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14048,10 +14048,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>406325</v>
+        <v>406414</v>
       </c>
       <c r="R136" t="n">
-        <v>6855978</v>
+        <v>6855915</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14110,10 +14110,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126600536</v>
+        <v>126600594</v>
       </c>
       <c r="B137" t="n">
-        <v>79598</v>
+        <v>57817</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14121,21 +14121,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14145,10 +14145,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>406521</v>
+        <v>406325</v>
       </c>
       <c r="R137" t="n">
-        <v>6855634</v>
+        <v>6855978</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14210,7 +14210,7 @@
         <v>126600607</v>
       </c>
       <c r="B138" t="n">
-        <v>97239</v>
+        <v>97314</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14304,10 +14304,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126600540</v>
+        <v>126600633</v>
       </c>
       <c r="B139" t="n">
-        <v>79598</v>
+        <v>78769</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14315,21 +14315,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14339,10 +14339,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>406582</v>
+        <v>406528</v>
       </c>
       <c r="R139" t="n">
-        <v>6855833</v>
+        <v>6855666</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14401,10 +14401,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126600667</v>
+        <v>126600540</v>
       </c>
       <c r="B140" t="n">
-        <v>78980</v>
+        <v>79629</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14412,21 +14412,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14436,10 +14436,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>406426</v>
+        <v>406582</v>
       </c>
       <c r="R140" t="n">
-        <v>6855972</v>
+        <v>6855833</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14501,7 +14501,7 @@
         <v>126600641</v>
       </c>
       <c r="B141" t="n">
-        <v>78738</v>
+        <v>78769</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14595,10 +14595,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126600547</v>
+        <v>126600667</v>
       </c>
       <c r="B142" t="n">
-        <v>79598</v>
+        <v>79011</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14606,21 +14606,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14630,10 +14630,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>406285</v>
+        <v>406426</v>
       </c>
       <c r="R142" t="n">
-        <v>6856129</v>
+        <v>6855972</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14692,10 +14692,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>126600633</v>
+        <v>126600547</v>
       </c>
       <c r="B143" t="n">
-        <v>78738</v>
+        <v>79629</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14703,21 +14703,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14727,10 +14727,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>406528</v>
+        <v>406285</v>
       </c>
       <c r="R143" t="n">
-        <v>6855666</v>
+        <v>6856129</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>

--- a/artfynd/A 29779-2025 artfynd.xlsx
+++ b/artfynd/A 29779-2025 artfynd.xlsx
@@ -3031,7 +3031,7 @@
         <v>126600584</v>
       </c>
       <c r="B23" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         <v>126600666</v>
       </c>
       <c r="B24" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3225,7 +3225,7 @@
         <v>126600545</v>
       </c>
       <c r="B25" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
         <v>126600688</v>
       </c>
       <c r="B26" t="n">
-        <v>78417</v>
+        <v>78420</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>126600668</v>
       </c>
       <c r="B27" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>126600621</v>
       </c>
       <c r="B29" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
         <v>126600627</v>
       </c>
       <c r="B30" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>126600623</v>
       </c>
       <c r="B31" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3905,32 +3905,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126600608</v>
+        <v>126600639</v>
       </c>
       <c r="B32" t="n">
-        <v>97320</v>
+        <v>78772</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221941</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3940,10 +3940,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>406378</v>
+        <v>406433</v>
       </c>
       <c r="R32" t="n">
-        <v>6856046</v>
+        <v>6856017</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4002,10 +4002,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126600620</v>
+        <v>126600635</v>
       </c>
       <c r="B33" t="n">
-        <v>78770</v>
+        <v>78772</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4013,21 +4013,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4037,10 +4037,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>406376</v>
+        <v>406535</v>
       </c>
       <c r="R33" t="n">
-        <v>6856016</v>
+        <v>6855969</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4099,32 +4099,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126600639</v>
+        <v>126600677</v>
       </c>
       <c r="B34" t="n">
-        <v>78769</v>
+        <v>92615</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>406433</v>
+        <v>406409</v>
       </c>
       <c r="R34" t="n">
-        <v>6856017</v>
+        <v>6855908</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4196,10 +4196,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126600635</v>
+        <v>126600556</v>
       </c>
       <c r="B35" t="n">
-        <v>78769</v>
+        <v>79632</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4207,21 +4207,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4231,10 +4231,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>406535</v>
+        <v>406389</v>
       </c>
       <c r="R35" t="n">
-        <v>6855969</v>
+        <v>6856021</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4293,32 +4293,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126600556</v>
+        <v>126600608</v>
       </c>
       <c r="B36" t="n">
-        <v>79629</v>
+        <v>97326</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4328,10 +4328,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>406389</v>
+        <v>406378</v>
       </c>
       <c r="R36" t="n">
-        <v>6856021</v>
+        <v>6856046</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4390,10 +4390,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126600679</v>
+        <v>126600620</v>
       </c>
       <c r="B37" t="n">
-        <v>78678</v>
+        <v>78773</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4401,21 +4401,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>406407</v>
+        <v>406376</v>
       </c>
       <c r="R37" t="n">
-        <v>6856127</v>
+        <v>6856016</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4487,32 +4487,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126600677</v>
+        <v>126600679</v>
       </c>
       <c r="B38" t="n">
-        <v>92609</v>
+        <v>78681</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4522,10 +4522,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>406409</v>
+        <v>406407</v>
       </c>
       <c r="R38" t="n">
-        <v>6855908</v>
+        <v>6856127</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4584,10 +4584,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126600561</v>
+        <v>126600626</v>
       </c>
       <c r="B39" t="n">
-        <v>79629</v>
+        <v>78773</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4595,21 +4595,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4619,10 +4619,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>406428</v>
+        <v>406473</v>
       </c>
       <c r="R39" t="n">
-        <v>6856010</v>
+        <v>6855839</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4681,10 +4681,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126600579</v>
+        <v>126600629</v>
       </c>
       <c r="B40" t="n">
-        <v>79629</v>
+        <v>78773</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4692,21 +4692,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4716,10 +4716,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>406421</v>
+        <v>406456</v>
       </c>
       <c r="R40" t="n">
-        <v>6855658</v>
+        <v>6855929</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4778,10 +4778,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126600553</v>
+        <v>126600561</v>
       </c>
       <c r="B41" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4813,10 +4813,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>406368</v>
+        <v>406428</v>
       </c>
       <c r="R41" t="n">
-        <v>6856013</v>
+        <v>6856010</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4875,10 +4875,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126600567</v>
+        <v>126600579</v>
       </c>
       <c r="B42" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4910,10 +4910,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>406471</v>
+        <v>406421</v>
       </c>
       <c r="R42" t="n">
-        <v>6855896</v>
+        <v>6855658</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4972,10 +4972,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126600626</v>
+        <v>126600553</v>
       </c>
       <c r="B43" t="n">
-        <v>78770</v>
+        <v>79632</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4983,21 +4983,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5007,10 +5007,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>406473</v>
+        <v>406368</v>
       </c>
       <c r="R43" t="n">
-        <v>6855839</v>
+        <v>6856013</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5069,10 +5069,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126600629</v>
+        <v>126600567</v>
       </c>
       <c r="B44" t="n">
-        <v>78770</v>
+        <v>79632</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5080,21 +5080,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5104,10 +5104,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>406456</v>
+        <v>406471</v>
       </c>
       <c r="R44" t="n">
-        <v>6855929</v>
+        <v>6855896</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5166,10 +5166,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126600656</v>
+        <v>126600619</v>
       </c>
       <c r="B45" t="n">
-        <v>79011</v>
+        <v>78773</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5177,21 +5177,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5201,10 +5201,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>406626</v>
+        <v>406365</v>
       </c>
       <c r="R45" t="n">
-        <v>6856024</v>
+        <v>6856013</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5263,10 +5263,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126600548</v>
+        <v>126600656</v>
       </c>
       <c r="B46" t="n">
-        <v>79629</v>
+        <v>79014</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5274,21 +5274,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5298,10 +5298,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>406278</v>
+        <v>406626</v>
       </c>
       <c r="R46" t="n">
-        <v>6855989</v>
+        <v>6856024</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5360,10 +5360,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126600559</v>
+        <v>126600548</v>
       </c>
       <c r="B47" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5395,10 +5395,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>406397</v>
+        <v>406278</v>
       </c>
       <c r="R47" t="n">
-        <v>6856067</v>
+        <v>6855989</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5457,10 +5457,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126600582</v>
+        <v>126600559</v>
       </c>
       <c r="B48" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5492,10 +5492,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>406432</v>
+        <v>406397</v>
       </c>
       <c r="R48" t="n">
-        <v>6855636</v>
+        <v>6856067</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5554,10 +5554,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126600572</v>
+        <v>126600582</v>
       </c>
       <c r="B49" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5589,10 +5589,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>406428</v>
+        <v>406432</v>
       </c>
       <c r="R49" t="n">
-        <v>6855941</v>
+        <v>6855636</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5651,10 +5651,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126600576</v>
+        <v>126600572</v>
       </c>
       <c r="B50" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5686,10 +5686,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>406439</v>
+        <v>406428</v>
       </c>
       <c r="R50" t="n">
-        <v>6855706</v>
+        <v>6855941</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5748,10 +5748,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126600619</v>
+        <v>126600576</v>
       </c>
       <c r="B51" t="n">
-        <v>78770</v>
+        <v>79632</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5759,21 +5759,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5783,10 +5783,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>406365</v>
+        <v>406439</v>
       </c>
       <c r="R51" t="n">
-        <v>6856013</v>
+        <v>6855706</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5848,7 +5848,7 @@
         <v>126600554</v>
       </c>
       <c r="B52" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5945,7 +5945,7 @@
         <v>126600558</v>
       </c>
       <c r="B53" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6039,10 +6039,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126600643</v>
+        <v>126600586</v>
       </c>
       <c r="B54" t="n">
-        <v>78769</v>
+        <v>91247</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6050,21 +6050,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>3242</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6074,10 +6074,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>406462</v>
+        <v>406331</v>
       </c>
       <c r="R54" t="n">
-        <v>6855914</v>
+        <v>6855997</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6136,10 +6136,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126600618</v>
+        <v>126600643</v>
       </c>
       <c r="B55" t="n">
-        <v>78770</v>
+        <v>78772</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6147,21 +6147,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6171,10 +6171,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>406323</v>
+        <v>406462</v>
       </c>
       <c r="R55" t="n">
-        <v>6856001</v>
+        <v>6855914</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6233,10 +6233,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126600586</v>
+        <v>126600618</v>
       </c>
       <c r="B56" t="n">
-        <v>91241</v>
+        <v>78773</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6244,21 +6244,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3242</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6268,10 +6268,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>406331</v>
+        <v>406323</v>
       </c>
       <c r="R56" t="n">
-        <v>6855997</v>
+        <v>6856001</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6330,32 +6330,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126600663</v>
+        <v>126600601</v>
       </c>
       <c r="B57" t="n">
-        <v>79011</v>
+        <v>98463</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6365,10 +6365,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>406523</v>
+        <v>406524</v>
       </c>
       <c r="R57" t="n">
-        <v>6856176</v>
+        <v>6856188</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6427,10 +6427,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126600645</v>
+        <v>126600590</v>
       </c>
       <c r="B58" t="n">
-        <v>78769</v>
+        <v>79603</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6438,21 +6438,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6462,10 +6462,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>406440</v>
+        <v>406293</v>
       </c>
       <c r="R58" t="n">
-        <v>6855714</v>
+        <v>6855983</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6524,32 +6524,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126600601</v>
+        <v>126600663</v>
       </c>
       <c r="B59" t="n">
-        <v>98457</v>
+        <v>79014</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6559,10 +6559,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>406524</v>
+        <v>406523</v>
       </c>
       <c r="R59" t="n">
-        <v>6856188</v>
+        <v>6856176</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6621,10 +6621,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126600590</v>
+        <v>126600645</v>
       </c>
       <c r="B60" t="n">
-        <v>79600</v>
+        <v>78772</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6632,21 +6632,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6656,10 +6656,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>406293</v>
+        <v>406440</v>
       </c>
       <c r="R60" t="n">
-        <v>6855983</v>
+        <v>6855714</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6718,10 +6718,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126600653</v>
+        <v>126600614</v>
       </c>
       <c r="B61" t="n">
-        <v>79011</v>
+        <v>78773</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6729,21 +6729,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6753,10 +6753,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>406536</v>
+        <v>406294</v>
       </c>
       <c r="R61" t="n">
-        <v>6855607</v>
+        <v>6856039</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6815,10 +6815,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126600636</v>
+        <v>126600653</v>
       </c>
       <c r="B62" t="n">
-        <v>78769</v>
+        <v>79014</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6826,21 +6826,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6850,10 +6850,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>406307</v>
+        <v>406536</v>
       </c>
       <c r="R62" t="n">
-        <v>6855949</v>
+        <v>6855607</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6912,10 +6912,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126600565</v>
+        <v>126600636</v>
       </c>
       <c r="B63" t="n">
-        <v>79629</v>
+        <v>78772</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6923,21 +6923,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6947,10 +6947,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>406485</v>
+        <v>406307</v>
       </c>
       <c r="R63" t="n">
-        <v>6855873</v>
+        <v>6855949</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7009,10 +7009,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126600684</v>
+        <v>126600565</v>
       </c>
       <c r="B64" t="n">
-        <v>78417</v>
+        <v>79632</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7020,21 +7020,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7044,10 +7044,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>406294</v>
+        <v>406485</v>
       </c>
       <c r="R64" t="n">
-        <v>6855983</v>
+        <v>6855873</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7106,10 +7106,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126600654</v>
+        <v>126600684</v>
       </c>
       <c r="B65" t="n">
-        <v>79011</v>
+        <v>78420</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7117,21 +7117,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7141,10 +7141,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>406623</v>
+        <v>406294</v>
       </c>
       <c r="R65" t="n">
-        <v>6855990</v>
+        <v>6855983</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7203,10 +7203,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126600614</v>
+        <v>126600654</v>
       </c>
       <c r="B66" t="n">
-        <v>78770</v>
+        <v>79014</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7214,21 +7214,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7238,10 +7238,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>406294</v>
+        <v>406623</v>
       </c>
       <c r="R66" t="n">
-        <v>6856039</v>
+        <v>6855990</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7303,7 +7303,7 @@
         <v>126600644</v>
       </c>
       <c r="B67" t="n">
-        <v>78769</v>
+        <v>78772</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         <v>126600664</v>
       </c>
       <c r="B68" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7497,7 +7497,7 @@
         <v>126600683</v>
       </c>
       <c r="B69" t="n">
-        <v>78417</v>
+        <v>78420</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7594,7 +7594,7 @@
         <v>126600624</v>
       </c>
       <c r="B70" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7691,7 +7691,7 @@
         <v>126600613</v>
       </c>
       <c r="B71" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7793,7 +7793,7 @@
         <v>126600551</v>
       </c>
       <c r="B72" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>126600555</v>
       </c>
       <c r="B73" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7987,7 +7987,7 @@
         <v>126600569</v>
       </c>
       <c r="B74" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
         <v>126600640</v>
       </c>
       <c r="B75" t="n">
-        <v>78769</v>
+        <v>78772</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8181,7 +8181,7 @@
         <v>126600552</v>
       </c>
       <c r="B76" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>126600537</v>
       </c>
       <c r="B77" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>126600631</v>
       </c>
       <c r="B78" t="n">
-        <v>80986</v>
+        <v>80989</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8472,7 +8472,7 @@
         <v>126600581</v>
       </c>
       <c r="B79" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>126600571</v>
       </c>
       <c r="B80" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         <v>126600680</v>
       </c>
       <c r="B81" t="n">
-        <v>78678</v>
+        <v>78681</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8763,7 +8763,7 @@
         <v>126600615</v>
       </c>
       <c r="B82" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8860,7 +8860,7 @@
         <v>126600652</v>
       </c>
       <c r="B83" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8962,7 +8962,7 @@
         <v>126600544</v>
       </c>
       <c r="B84" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9059,7 +9059,7 @@
         <v>126600560</v>
       </c>
       <c r="B85" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9156,7 +9156,7 @@
         <v>126600546</v>
       </c>
       <c r="B86" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>126600678</v>
       </c>
       <c r="B87" t="n">
-        <v>78678</v>
+        <v>78681</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9347,10 +9347,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126600577</v>
+        <v>126600611</v>
       </c>
       <c r="B88" t="n">
-        <v>79629</v>
+        <v>92808</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9358,21 +9358,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9382,10 +9382,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>406461</v>
+        <v>406433</v>
       </c>
       <c r="R88" t="n">
-        <v>6855692</v>
+        <v>6855894</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9444,32 +9444,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126600591</v>
+        <v>126600577</v>
       </c>
       <c r="B89" t="n">
-        <v>91284</v>
+        <v>79632</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9479,10 +9479,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>406266</v>
+        <v>406461</v>
       </c>
       <c r="R89" t="n">
-        <v>6856149</v>
+        <v>6855692</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9541,32 +9541,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126600660</v>
+        <v>126600591</v>
       </c>
       <c r="B90" t="n">
-        <v>79011</v>
+        <v>91290</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9576,10 +9576,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>406521</v>
+        <v>406266</v>
       </c>
       <c r="R90" t="n">
-        <v>6856195</v>
+        <v>6856149</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9638,10 +9638,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126600657</v>
+        <v>126600660</v>
       </c>
       <c r="B91" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9673,10 +9673,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>406513</v>
+        <v>406521</v>
       </c>
       <c r="R91" t="n">
-        <v>6856139</v>
+        <v>6856195</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9735,10 +9735,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126600543</v>
+        <v>126600657</v>
       </c>
       <c r="B92" t="n">
-        <v>79629</v>
+        <v>79014</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9746,21 +9746,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9770,10 +9770,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>406586</v>
+        <v>406513</v>
       </c>
       <c r="R92" t="n">
-        <v>6856018</v>
+        <v>6856139</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9832,10 +9832,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126600611</v>
+        <v>126600543</v>
       </c>
       <c r="B93" t="n">
-        <v>92802</v>
+        <v>79632</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9843,21 +9843,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9867,10 +9867,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>406433</v>
+        <v>406586</v>
       </c>
       <c r="R93" t="n">
-        <v>6855894</v>
+        <v>6856018</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9932,7 +9932,7 @@
         <v>126600628</v>
       </c>
       <c r="B94" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10029,7 +10029,7 @@
         <v>126600630</v>
       </c>
       <c r="B95" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10123,10 +10123,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126600541</v>
+        <v>126600616</v>
       </c>
       <c r="B96" t="n">
-        <v>79629</v>
+        <v>78773</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10134,21 +10134,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10158,10 +10158,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>406596</v>
+        <v>406293</v>
       </c>
       <c r="R96" t="n">
-        <v>6855897</v>
+        <v>6855983</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10220,10 +10220,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126600585</v>
+        <v>126600589</v>
       </c>
       <c r="B97" t="n">
-        <v>79629</v>
+        <v>79603</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10231,21 +10231,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10255,10 +10255,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>406436</v>
+        <v>406271</v>
       </c>
       <c r="R97" t="n">
-        <v>6855599</v>
+        <v>6856003</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10317,10 +10317,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126600575</v>
+        <v>126600681</v>
       </c>
       <c r="B98" t="n">
-        <v>79629</v>
+        <v>78681</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10328,21 +10328,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10352,10 +10352,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>406441</v>
+        <v>406422</v>
       </c>
       <c r="R98" t="n">
-        <v>6855713</v>
+        <v>6856055</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10414,10 +10414,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126600563</v>
+        <v>126600541</v>
       </c>
       <c r="B99" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10449,10 +10449,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>406460</v>
+        <v>406596</v>
       </c>
       <c r="R99" t="n">
-        <v>6855846</v>
+        <v>6855897</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10511,10 +10511,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126600580</v>
+        <v>126600585</v>
       </c>
       <c r="B100" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10546,10 +10546,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>406422</v>
+        <v>406436</v>
       </c>
       <c r="R100" t="n">
-        <v>6855652</v>
+        <v>6855599</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10608,10 +10608,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126600681</v>
+        <v>126600575</v>
       </c>
       <c r="B101" t="n">
-        <v>78678</v>
+        <v>79632</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10619,21 +10619,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10643,10 +10643,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>406422</v>
+        <v>406441</v>
       </c>
       <c r="R101" t="n">
-        <v>6856055</v>
+        <v>6855713</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10705,10 +10705,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126600616</v>
+        <v>126600563</v>
       </c>
       <c r="B102" t="n">
-        <v>78770</v>
+        <v>79632</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10716,21 +10716,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10740,10 +10740,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>406293</v>
+        <v>406460</v>
       </c>
       <c r="R102" t="n">
-        <v>6855983</v>
+        <v>6855846</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10802,10 +10802,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126600589</v>
+        <v>126600580</v>
       </c>
       <c r="B103" t="n">
-        <v>79600</v>
+        <v>79632</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10813,21 +10813,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10837,10 +10837,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>406271</v>
+        <v>406422</v>
       </c>
       <c r="R103" t="n">
-        <v>6856003</v>
+        <v>6855652</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10902,7 +10902,7 @@
         <v>126600622</v>
       </c>
       <c r="B104" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>126600637</v>
       </c>
       <c r="B105" t="n">
-        <v>78769</v>
+        <v>78772</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11096,7 +11096,7 @@
         <v>126600574</v>
       </c>
       <c r="B106" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11193,7 +11193,7 @@
         <v>126600655</v>
       </c>
       <c r="B107" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11290,7 +11290,7 @@
         <v>126600587</v>
       </c>
       <c r="B108" t="n">
-        <v>75135</v>
+        <v>75138</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11387,7 +11387,7 @@
         <v>126600557</v>
       </c>
       <c r="B109" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11484,7 +11484,7 @@
         <v>126600606</v>
       </c>
       <c r="B110" t="n">
-        <v>97314</v>
+        <v>97320</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11578,10 +11578,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126600573</v>
+        <v>126600617</v>
       </c>
       <c r="B111" t="n">
-        <v>79629</v>
+        <v>78773</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11589,21 +11589,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11613,10 +11613,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>406409</v>
+        <v>406303</v>
       </c>
       <c r="R111" t="n">
-        <v>6855915</v>
+        <v>6855965</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11675,10 +11675,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126600570</v>
+        <v>126600573</v>
       </c>
       <c r="B112" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11710,10 +11710,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>406442</v>
+        <v>406409</v>
       </c>
       <c r="R112" t="n">
-        <v>6855938</v>
+        <v>6855915</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11772,10 +11772,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126600651</v>
+        <v>126600570</v>
       </c>
       <c r="B113" t="n">
-        <v>91337</v>
+        <v>79632</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11783,21 +11783,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11807,10 +11807,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>406515</v>
+        <v>406442</v>
       </c>
       <c r="R113" t="n">
-        <v>6856173</v>
+        <v>6855938</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11869,10 +11869,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126600650</v>
+        <v>126600651</v>
       </c>
       <c r="B114" t="n">
-        <v>91337</v>
+        <v>91343</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11904,10 +11904,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>406523</v>
+        <v>406515</v>
       </c>
       <c r="R114" t="n">
-        <v>6856161</v>
+        <v>6856173</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11966,10 +11966,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126600542</v>
+        <v>126600650</v>
       </c>
       <c r="B115" t="n">
-        <v>79629</v>
+        <v>91343</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11977,21 +11977,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>5432</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12001,10 +12001,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>406587</v>
+        <v>406523</v>
       </c>
       <c r="R115" t="n">
-        <v>6855895</v>
+        <v>6856161</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12063,10 +12063,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126600605</v>
+        <v>126600542</v>
       </c>
       <c r="B116" t="n">
-        <v>57657</v>
+        <v>79632</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12074,39 +12074,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Öjvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>406627</v>
+        <v>406587</v>
       </c>
       <c r="R116" t="n">
-        <v>6856015</v>
+        <v>6855895</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12139,11 +12134,6 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-07-11</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12170,10 +12160,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126600617</v>
+        <v>126600605</v>
       </c>
       <c r="B117" t="n">
-        <v>78770</v>
+        <v>57657</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12181,34 +12171,39 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Öjvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>406303</v>
+        <v>406627</v>
       </c>
       <c r="R117" t="n">
-        <v>6855965</v>
+        <v>6856015</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12241,6 +12236,11 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12270,7 +12270,7 @@
         <v>126600658</v>
       </c>
       <c r="B118" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12367,7 +12367,7 @@
         <v>126600549</v>
       </c>
       <c r="B119" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12464,7 +12464,7 @@
         <v>126600673</v>
       </c>
       <c r="B120" t="n">
-        <v>92609</v>
+        <v>92615</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12558,10 +12558,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126600642</v>
+        <v>126600682</v>
       </c>
       <c r="B121" t="n">
-        <v>78769</v>
+        <v>78681</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12569,21 +12569,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12593,10 +12593,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>406485</v>
+        <v>406425</v>
       </c>
       <c r="R121" t="n">
-        <v>6855875</v>
+        <v>6855965</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12655,10 +12655,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126600632</v>
+        <v>126600642</v>
       </c>
       <c r="B122" t="n">
-        <v>78769</v>
+        <v>78772</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12690,10 +12690,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>406502</v>
+        <v>406485</v>
       </c>
       <c r="R122" t="n">
-        <v>6855622</v>
+        <v>6855875</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12752,10 +12752,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126600535</v>
+        <v>126600632</v>
       </c>
       <c r="B123" t="n">
-        <v>79629</v>
+        <v>78772</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12763,21 +12763,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12849,32 +12849,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126600665</v>
+        <v>126600675</v>
       </c>
       <c r="B124" t="n">
-        <v>79011</v>
+        <v>92615</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12884,10 +12884,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>406499</v>
+        <v>406442</v>
       </c>
       <c r="R124" t="n">
-        <v>6856166</v>
+        <v>6855951</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12946,10 +12946,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126600634</v>
+        <v>126600535</v>
       </c>
       <c r="B125" t="n">
-        <v>78769</v>
+        <v>79632</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12957,21 +12957,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12981,10 +12981,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>406580</v>
+        <v>406502</v>
       </c>
       <c r="R125" t="n">
-        <v>6855911</v>
+        <v>6855622</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13043,10 +13043,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126600562</v>
+        <v>126600665</v>
       </c>
       <c r="B126" t="n">
-        <v>79629</v>
+        <v>79014</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13054,21 +13054,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13078,10 +13078,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>406422</v>
+        <v>406499</v>
       </c>
       <c r="R126" t="n">
-        <v>6855969</v>
+        <v>6856166</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13140,10 +13140,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126600682</v>
+        <v>126600634</v>
       </c>
       <c r="B127" t="n">
-        <v>78678</v>
+        <v>78772</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13151,21 +13151,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13175,10 +13175,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>406425</v>
+        <v>406580</v>
       </c>
       <c r="R127" t="n">
-        <v>6855965</v>
+        <v>6855911</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13237,32 +13237,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126600675</v>
+        <v>126600562</v>
       </c>
       <c r="B128" t="n">
-        <v>92609</v>
+        <v>79632</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13272,10 +13272,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>406442</v>
+        <v>406422</v>
       </c>
       <c r="R128" t="n">
-        <v>6855951</v>
+        <v>6855969</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13337,7 +13337,7 @@
         <v>126600672</v>
       </c>
       <c r="B129" t="n">
-        <v>92609</v>
+        <v>92615</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13434,7 +13434,7 @@
         <v>126600568</v>
       </c>
       <c r="B130" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13531,7 +13531,7 @@
         <v>126600538</v>
       </c>
       <c r="B131" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13628,7 +13628,7 @@
         <v>126600625</v>
       </c>
       <c r="B132" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13722,10 +13722,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126600638</v>
+        <v>126600594</v>
       </c>
       <c r="B133" t="n">
-        <v>78769</v>
+        <v>57817</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13733,21 +13733,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13757,10 +13757,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>406379</v>
+        <v>406325</v>
       </c>
       <c r="R133" t="n">
-        <v>6856040</v>
+        <v>6855978</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13819,32 +13819,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126600566</v>
+        <v>126600676</v>
       </c>
       <c r="B134" t="n">
-        <v>79629</v>
+        <v>92615</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13854,10 +13854,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>406482</v>
+        <v>406414</v>
       </c>
       <c r="R134" t="n">
-        <v>6855876</v>
+        <v>6855915</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13916,10 +13916,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126600536</v>
+        <v>126600638</v>
       </c>
       <c r="B135" t="n">
-        <v>79629</v>
+        <v>78772</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13927,21 +13927,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -13951,10 +13951,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>406521</v>
+        <v>406379</v>
       </c>
       <c r="R135" t="n">
-        <v>6855634</v>
+        <v>6856040</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14013,32 +14013,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126600676</v>
+        <v>126600566</v>
       </c>
       <c r="B136" t="n">
-        <v>92609</v>
+        <v>79632</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14048,10 +14048,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>406414</v>
+        <v>406482</v>
       </c>
       <c r="R136" t="n">
-        <v>6855915</v>
+        <v>6855876</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14110,10 +14110,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126600594</v>
+        <v>126600536</v>
       </c>
       <c r="B137" t="n">
-        <v>57817</v>
+        <v>79632</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14121,21 +14121,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14145,10 +14145,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>406325</v>
+        <v>406521</v>
       </c>
       <c r="R137" t="n">
-        <v>6855978</v>
+        <v>6855634</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14207,32 +14207,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126600607</v>
+        <v>126600633</v>
       </c>
       <c r="B138" t="n">
-        <v>97314</v>
+        <v>78772</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>221945</v>
+        <v>6446</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14242,10 +14242,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>406576</v>
+        <v>406528</v>
       </c>
       <c r="R138" t="n">
-        <v>6856013</v>
+        <v>6855666</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14304,10 +14304,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126600633</v>
+        <v>126600540</v>
       </c>
       <c r="B139" t="n">
-        <v>78769</v>
+        <v>79632</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14315,21 +14315,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14339,10 +14339,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>406528</v>
+        <v>406582</v>
       </c>
       <c r="R139" t="n">
-        <v>6855666</v>
+        <v>6855833</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14401,10 +14401,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126600540</v>
+        <v>126600641</v>
       </c>
       <c r="B140" t="n">
-        <v>79629</v>
+        <v>78772</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14412,21 +14412,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14436,10 +14436,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>406582</v>
+        <v>406491</v>
       </c>
       <c r="R140" t="n">
-        <v>6855833</v>
+        <v>6855856</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14498,10 +14498,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126600641</v>
+        <v>126600667</v>
       </c>
       <c r="B141" t="n">
-        <v>78769</v>
+        <v>79014</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14509,21 +14509,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14533,10 +14533,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>406491</v>
+        <v>406426</v>
       </c>
       <c r="R141" t="n">
-        <v>6855856</v>
+        <v>6855972</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14595,10 +14595,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126600667</v>
+        <v>126600547</v>
       </c>
       <c r="B142" t="n">
-        <v>79011</v>
+        <v>79632</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14606,21 +14606,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14630,10 +14630,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>406426</v>
+        <v>406285</v>
       </c>
       <c r="R142" t="n">
-        <v>6855972</v>
+        <v>6856129</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14692,32 +14692,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>126600547</v>
+        <v>126600607</v>
       </c>
       <c r="B143" t="n">
-        <v>79629</v>
+        <v>97320</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6453</v>
+        <v>221945</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14727,10 +14727,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>406285</v>
+        <v>406576</v>
       </c>
       <c r="R143" t="n">
-        <v>6856129</v>
+        <v>6856013</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>

--- a/artfynd/A 29779-2025 artfynd.xlsx
+++ b/artfynd/A 29779-2025 artfynd.xlsx
@@ -3125,10 +3125,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126600666</v>
+        <v>126600545</v>
       </c>
       <c r="B24" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3136,21 +3136,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3160,10 +3160,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>406495</v>
+        <v>406516</v>
       </c>
       <c r="R24" t="n">
-        <v>6856163</v>
+        <v>6856086</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3222,10 +3222,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126600545</v>
+        <v>126600688</v>
       </c>
       <c r="B25" t="n">
-        <v>79632</v>
+        <v>78420</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3233,21 +3233,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3257,10 +3257,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>406516</v>
+        <v>406442</v>
       </c>
       <c r="R25" t="n">
-        <v>6856086</v>
+        <v>6855707</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3319,10 +3319,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126600688</v>
+        <v>126600666</v>
       </c>
       <c r="B26" t="n">
-        <v>78420</v>
+        <v>79014</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3330,21 +3330,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3354,10 +3354,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>406442</v>
+        <v>406495</v>
       </c>
       <c r="R26" t="n">
-        <v>6855707</v>
+        <v>6856163</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3513,10 +3513,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126600593</v>
+        <v>126600621</v>
       </c>
       <c r="B28" t="n">
-        <v>57817</v>
+        <v>78773</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3524,38 +3524,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Öjvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>406292</v>
+        <v>406382</v>
       </c>
       <c r="R28" t="n">
-        <v>6856034</v>
+        <v>6856055</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3614,10 +3610,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126600621</v>
+        <v>126600593</v>
       </c>
       <c r="B29" t="n">
-        <v>78773</v>
+        <v>57817</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3625,34 +3621,38 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Öjvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>406382</v>
+        <v>406292</v>
       </c>
       <c r="R29" t="n">
-        <v>6856055</v>
+        <v>6856034</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4099,32 +4099,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126600677</v>
+        <v>126600556</v>
       </c>
       <c r="B34" t="n">
-        <v>92615</v>
+        <v>79632</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>406409</v>
+        <v>406389</v>
       </c>
       <c r="R34" t="n">
-        <v>6855908</v>
+        <v>6856021</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4196,10 +4196,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126600556</v>
+        <v>126600679</v>
       </c>
       <c r="B35" t="n">
-        <v>79632</v>
+        <v>78681</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4207,21 +4207,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4231,10 +4231,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>406389</v>
+        <v>406407</v>
       </c>
       <c r="R35" t="n">
-        <v>6856021</v>
+        <v>6856127</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4293,10 +4293,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126600608</v>
+        <v>126600677</v>
       </c>
       <c r="B36" t="n">
-        <v>97326</v>
+        <v>92615</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4304,21 +4304,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4328,10 +4328,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>406378</v>
+        <v>406409</v>
       </c>
       <c r="R36" t="n">
-        <v>6856046</v>
+        <v>6855908</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4487,32 +4487,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126600679</v>
+        <v>126600608</v>
       </c>
       <c r="B38" t="n">
-        <v>78681</v>
+        <v>97326</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>353</v>
+        <v>221941</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4522,10 +4522,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>406407</v>
+        <v>406378</v>
       </c>
       <c r="R38" t="n">
-        <v>6856127</v>
+        <v>6856046</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4584,10 +4584,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126600626</v>
+        <v>126600561</v>
       </c>
       <c r="B39" t="n">
-        <v>78773</v>
+        <v>79632</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4595,21 +4595,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4619,10 +4619,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>406473</v>
+        <v>406428</v>
       </c>
       <c r="R39" t="n">
-        <v>6855839</v>
+        <v>6856010</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4681,10 +4681,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126600629</v>
+        <v>126600579</v>
       </c>
       <c r="B40" t="n">
-        <v>78773</v>
+        <v>79632</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4692,21 +4692,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4716,10 +4716,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>406456</v>
+        <v>406421</v>
       </c>
       <c r="R40" t="n">
-        <v>6855929</v>
+        <v>6855658</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4778,7 +4778,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126600561</v>
+        <v>126600553</v>
       </c>
       <c r="B41" t="n">
         <v>79632</v>
@@ -4813,10 +4813,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>406428</v>
+        <v>406368</v>
       </c>
       <c r="R41" t="n">
-        <v>6856010</v>
+        <v>6856013</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4875,7 +4875,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126600579</v>
+        <v>126600567</v>
       </c>
       <c r="B42" t="n">
         <v>79632</v>
@@ -4910,10 +4910,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>406421</v>
+        <v>406471</v>
       </c>
       <c r="R42" t="n">
-        <v>6855658</v>
+        <v>6855896</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4972,10 +4972,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126600553</v>
+        <v>126600626</v>
       </c>
       <c r="B43" t="n">
-        <v>79632</v>
+        <v>78773</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4983,21 +4983,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5007,10 +5007,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>406368</v>
+        <v>406473</v>
       </c>
       <c r="R43" t="n">
-        <v>6856013</v>
+        <v>6855839</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5069,10 +5069,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126600567</v>
+        <v>126600629</v>
       </c>
       <c r="B44" t="n">
-        <v>79632</v>
+        <v>78773</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5080,21 +5080,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5104,10 +5104,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>406471</v>
+        <v>406456</v>
       </c>
       <c r="R44" t="n">
-        <v>6855896</v>
+        <v>6855929</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5166,10 +5166,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126600619</v>
+        <v>126600656</v>
       </c>
       <c r="B45" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5177,21 +5177,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5201,10 +5201,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>406365</v>
+        <v>406626</v>
       </c>
       <c r="R45" t="n">
-        <v>6856013</v>
+        <v>6856024</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5263,10 +5263,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126600656</v>
+        <v>126600548</v>
       </c>
       <c r="B46" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5274,21 +5274,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5298,10 +5298,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>406626</v>
+        <v>406278</v>
       </c>
       <c r="R46" t="n">
-        <v>6856024</v>
+        <v>6855989</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5360,7 +5360,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126600548</v>
+        <v>126600559</v>
       </c>
       <c r="B47" t="n">
         <v>79632</v>
@@ -5395,10 +5395,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>406278</v>
+        <v>406397</v>
       </c>
       <c r="R47" t="n">
-        <v>6855989</v>
+        <v>6856067</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5457,7 +5457,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126600559</v>
+        <v>126600582</v>
       </c>
       <c r="B48" t="n">
         <v>79632</v>
@@ -5492,10 +5492,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>406397</v>
+        <v>406432</v>
       </c>
       <c r="R48" t="n">
-        <v>6856067</v>
+        <v>6855636</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5554,7 +5554,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126600582</v>
+        <v>126600572</v>
       </c>
       <c r="B49" t="n">
         <v>79632</v>
@@ -5589,10 +5589,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>406432</v>
+        <v>406428</v>
       </c>
       <c r="R49" t="n">
-        <v>6855636</v>
+        <v>6855941</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5651,7 +5651,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126600572</v>
+        <v>126600576</v>
       </c>
       <c r="B50" t="n">
         <v>79632</v>
@@ -5686,10 +5686,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>406428</v>
+        <v>406439</v>
       </c>
       <c r="R50" t="n">
-        <v>6855941</v>
+        <v>6855706</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5748,10 +5748,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126600576</v>
+        <v>126600619</v>
       </c>
       <c r="B51" t="n">
-        <v>79632</v>
+        <v>78773</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5759,21 +5759,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5783,10 +5783,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>406439</v>
+        <v>406365</v>
       </c>
       <c r="R51" t="n">
-        <v>6855706</v>
+        <v>6856013</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5845,10 +5845,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126600554</v>
+        <v>126600586</v>
       </c>
       <c r="B52" t="n">
-        <v>79632</v>
+        <v>91247</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5856,21 +5856,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>3242</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5880,10 +5880,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>406376</v>
+        <v>406331</v>
       </c>
       <c r="R52" t="n">
-        <v>6856016</v>
+        <v>6855997</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5942,10 +5942,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126600558</v>
+        <v>126600618</v>
       </c>
       <c r="B53" t="n">
-        <v>79632</v>
+        <v>78773</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5953,21 +5953,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5977,10 +5977,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>406382</v>
+        <v>406323</v>
       </c>
       <c r="R53" t="n">
-        <v>6856055</v>
+        <v>6856001</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6039,10 +6039,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126600586</v>
+        <v>126600554</v>
       </c>
       <c r="B54" t="n">
-        <v>91247</v>
+        <v>79632</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6050,21 +6050,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3242</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6074,10 +6074,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>406331</v>
+        <v>406376</v>
       </c>
       <c r="R54" t="n">
-        <v>6855997</v>
+        <v>6856016</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6136,10 +6136,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126600643</v>
+        <v>126600558</v>
       </c>
       <c r="B55" t="n">
-        <v>78772</v>
+        <v>79632</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6147,21 +6147,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6171,10 +6171,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>406462</v>
+        <v>406382</v>
       </c>
       <c r="R55" t="n">
-        <v>6855914</v>
+        <v>6856055</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6233,10 +6233,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126600618</v>
+        <v>126600643</v>
       </c>
       <c r="B56" t="n">
-        <v>78773</v>
+        <v>78772</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6244,21 +6244,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6268,10 +6268,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>406323</v>
+        <v>406462</v>
       </c>
       <c r="R56" t="n">
-        <v>6856001</v>
+        <v>6855914</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6330,32 +6330,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126600601</v>
+        <v>126600663</v>
       </c>
       <c r="B57" t="n">
-        <v>98463</v>
+        <v>79014</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6365,10 +6365,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>406524</v>
+        <v>406523</v>
       </c>
       <c r="R57" t="n">
-        <v>6856188</v>
+        <v>6856176</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6427,10 +6427,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126600590</v>
+        <v>126600645</v>
       </c>
       <c r="B58" t="n">
-        <v>79603</v>
+        <v>78772</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6438,21 +6438,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6462,10 +6462,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>406293</v>
+        <v>406440</v>
       </c>
       <c r="R58" t="n">
-        <v>6855983</v>
+        <v>6855714</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6524,10 +6524,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126600663</v>
+        <v>126600590</v>
       </c>
       <c r="B59" t="n">
-        <v>79014</v>
+        <v>79603</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6535,21 +6535,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6559,10 +6559,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>406523</v>
+        <v>406293</v>
       </c>
       <c r="R59" t="n">
-        <v>6856176</v>
+        <v>6855983</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6621,32 +6621,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126600645</v>
+        <v>126600601</v>
       </c>
       <c r="B60" t="n">
-        <v>78772</v>
+        <v>98463</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6446</v>
+        <v>221952</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6656,10 +6656,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>406440</v>
+        <v>406524</v>
       </c>
       <c r="R60" t="n">
-        <v>6855714</v>
+        <v>6856188</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6718,10 +6718,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126600614</v>
+        <v>126600653</v>
       </c>
       <c r="B61" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6729,21 +6729,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6753,10 +6753,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>406294</v>
+        <v>406536</v>
       </c>
       <c r="R61" t="n">
-        <v>6856039</v>
+        <v>6855607</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6815,7 +6815,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126600653</v>
+        <v>126600654</v>
       </c>
       <c r="B62" t="n">
         <v>79014</v>
@@ -6850,10 +6850,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>406536</v>
+        <v>406623</v>
       </c>
       <c r="R62" t="n">
-        <v>6855607</v>
+        <v>6855990</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6912,10 +6912,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126600636</v>
+        <v>126600614</v>
       </c>
       <c r="B63" t="n">
-        <v>78772</v>
+        <v>78773</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6923,21 +6923,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6947,10 +6947,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>406307</v>
+        <v>406294</v>
       </c>
       <c r="R63" t="n">
-        <v>6855949</v>
+        <v>6856039</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7009,10 +7009,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126600565</v>
+        <v>126600636</v>
       </c>
       <c r="B64" t="n">
-        <v>79632</v>
+        <v>78772</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7020,21 +7020,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7044,10 +7044,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>406485</v>
+        <v>406307</v>
       </c>
       <c r="R64" t="n">
-        <v>6855873</v>
+        <v>6855949</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7106,10 +7106,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126600684</v>
+        <v>126600565</v>
       </c>
       <c r="B65" t="n">
-        <v>78420</v>
+        <v>79632</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7117,21 +7117,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7141,10 +7141,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>406294</v>
+        <v>406485</v>
       </c>
       <c r="R65" t="n">
-        <v>6855983</v>
+        <v>6855873</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7203,10 +7203,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126600654</v>
+        <v>126600684</v>
       </c>
       <c r="B66" t="n">
-        <v>79014</v>
+        <v>78420</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7214,21 +7214,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7238,10 +7238,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>406623</v>
+        <v>406294</v>
       </c>
       <c r="R66" t="n">
-        <v>6855990</v>
+        <v>6855983</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7300,10 +7300,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126600644</v>
+        <v>126600624</v>
       </c>
       <c r="B67" t="n">
-        <v>78772</v>
+        <v>78773</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7311,21 +7311,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7335,10 +7335,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>406406</v>
+        <v>406429</v>
       </c>
       <c r="R67" t="n">
-        <v>6855855</v>
+        <v>6856032</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7397,10 +7397,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126600664</v>
+        <v>126600613</v>
       </c>
       <c r="B68" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7408,21 +7408,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7432,10 +7432,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>406512</v>
+        <v>406469</v>
       </c>
       <c r="R68" t="n">
-        <v>6856169</v>
+        <v>6855892</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7468,6 +7468,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>På stubbe med 3 brandljud</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7494,10 +7499,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126600683</v>
+        <v>126600664</v>
       </c>
       <c r="B69" t="n">
-        <v>78420</v>
+        <v>79014</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7505,21 +7510,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7529,10 +7534,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>406500</v>
+        <v>406512</v>
       </c>
       <c r="R69" t="n">
-        <v>6856028</v>
+        <v>6856169</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7591,10 +7596,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126600624</v>
+        <v>126600644</v>
       </c>
       <c r="B70" t="n">
-        <v>78773</v>
+        <v>78772</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7602,21 +7607,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7626,10 +7631,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>406429</v>
+        <v>406406</v>
       </c>
       <c r="R70" t="n">
-        <v>6856032</v>
+        <v>6855855</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7688,10 +7693,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126600613</v>
+        <v>126600683</v>
       </c>
       <c r="B71" t="n">
-        <v>78773</v>
+        <v>78420</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7699,21 +7704,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7723,10 +7728,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>406469</v>
+        <v>406500</v>
       </c>
       <c r="R71" t="n">
-        <v>6855892</v>
+        <v>6856028</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7759,11 +7764,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-07-11</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>På stubbe med 3 brandljud</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8469,10 +8469,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126600581</v>
+        <v>126600615</v>
       </c>
       <c r="B79" t="n">
-        <v>79632</v>
+        <v>78773</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8480,21 +8480,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8504,10 +8504,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>406418</v>
+        <v>406271</v>
       </c>
       <c r="R79" t="n">
-        <v>6855644</v>
+        <v>6856003</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8566,7 +8566,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126600571</v>
+        <v>126600581</v>
       </c>
       <c r="B80" t="n">
         <v>79632</v>
@@ -8601,10 +8601,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>406431</v>
+        <v>406418</v>
       </c>
       <c r="R80" t="n">
-        <v>6855941</v>
+        <v>6855644</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8760,10 +8760,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126600615</v>
+        <v>126600571</v>
       </c>
       <c r="B82" t="n">
-        <v>78773</v>
+        <v>79632</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8771,21 +8771,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8795,10 +8795,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>406271</v>
+        <v>406431</v>
       </c>
       <c r="R82" t="n">
-        <v>6856003</v>
+        <v>6855941</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8857,10 +8857,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126600652</v>
+        <v>126600544</v>
       </c>
       <c r="B83" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8868,21 +8868,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8892,10 +8892,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>406459</v>
+        <v>406538</v>
       </c>
       <c r="R83" t="n">
-        <v>6855873</v>
+        <v>6855980</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8928,11 +8928,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-07-11</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>På gammeltall utan hänsynsmarkering</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8959,7 +8954,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126600544</v>
+        <v>126600560</v>
       </c>
       <c r="B84" t="n">
         <v>79632</v>
@@ -8994,10 +8989,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>406538</v>
+        <v>406434</v>
       </c>
       <c r="R84" t="n">
-        <v>6855980</v>
+        <v>6856017</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9056,7 +9051,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126600560</v>
+        <v>126600546</v>
       </c>
       <c r="B85" t="n">
         <v>79632</v>
@@ -9091,10 +9086,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>406434</v>
+        <v>406343</v>
       </c>
       <c r="R85" t="n">
-        <v>6856017</v>
+        <v>6856059</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9153,10 +9148,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126600546</v>
+        <v>126600678</v>
       </c>
       <c r="B86" t="n">
-        <v>79632</v>
+        <v>78681</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9164,21 +9159,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9188,10 +9183,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>406343</v>
+        <v>406585</v>
       </c>
       <c r="R86" t="n">
-        <v>6856059</v>
+        <v>6856016</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9250,10 +9245,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126600678</v>
+        <v>126600652</v>
       </c>
       <c r="B87" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9261,21 +9256,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9285,10 +9280,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>406585</v>
+        <v>406459</v>
       </c>
       <c r="R87" t="n">
-        <v>6856016</v>
+        <v>6855873</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9321,6 +9316,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>På gammeltall utan hänsynsmarkering</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9347,10 +9347,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126600611</v>
+        <v>126600577</v>
       </c>
       <c r="B88" t="n">
-        <v>92808</v>
+        <v>79632</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9358,21 +9358,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9382,10 +9382,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>406433</v>
+        <v>406461</v>
       </c>
       <c r="R88" t="n">
-        <v>6855894</v>
+        <v>6855692</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9444,7 +9444,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126600577</v>
+        <v>126600543</v>
       </c>
       <c r="B89" t="n">
         <v>79632</v>
@@ -9479,10 +9479,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>406461</v>
+        <v>406586</v>
       </c>
       <c r="R89" t="n">
-        <v>6855692</v>
+        <v>6856018</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9541,32 +9541,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126600591</v>
+        <v>126600628</v>
       </c>
       <c r="B90" t="n">
-        <v>91290</v>
+        <v>78773</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5447</v>
+        <v>228912</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9576,10 +9576,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>406266</v>
+        <v>406471</v>
       </c>
       <c r="R90" t="n">
-        <v>6856149</v>
+        <v>6855896</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9638,10 +9638,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126600660</v>
+        <v>126600630</v>
       </c>
       <c r="B91" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9649,21 +9649,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9673,10 +9673,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>406521</v>
+        <v>406428</v>
       </c>
       <c r="R91" t="n">
-        <v>6856195</v>
+        <v>6855941</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9735,32 +9735,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126600657</v>
+        <v>126600591</v>
       </c>
       <c r="B92" t="n">
-        <v>79014</v>
+        <v>91290</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9770,10 +9770,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>406513</v>
+        <v>406266</v>
       </c>
       <c r="R92" t="n">
-        <v>6856139</v>
+        <v>6856149</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9832,10 +9832,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126600543</v>
+        <v>126600611</v>
       </c>
       <c r="B93" t="n">
-        <v>79632</v>
+        <v>92808</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9843,21 +9843,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9867,10 +9867,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>406586</v>
+        <v>406433</v>
       </c>
       <c r="R93" t="n">
-        <v>6856018</v>
+        <v>6855894</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9929,10 +9929,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126600628</v>
+        <v>126600660</v>
       </c>
       <c r="B94" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9940,21 +9940,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9964,10 +9964,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>406471</v>
+        <v>406521</v>
       </c>
       <c r="R94" t="n">
-        <v>6855896</v>
+        <v>6856195</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10026,10 +10026,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126600630</v>
+        <v>126600657</v>
       </c>
       <c r="B95" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10037,21 +10037,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10061,10 +10061,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>406428</v>
+        <v>406513</v>
       </c>
       <c r="R95" t="n">
-        <v>6855941</v>
+        <v>6856139</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10123,10 +10123,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126600616</v>
+        <v>126600541</v>
       </c>
       <c r="B96" t="n">
-        <v>78773</v>
+        <v>79632</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10134,21 +10134,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10158,10 +10158,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>406293</v>
+        <v>406596</v>
       </c>
       <c r="R96" t="n">
-        <v>6855983</v>
+        <v>6855897</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10220,10 +10220,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126600589</v>
+        <v>126600585</v>
       </c>
       <c r="B97" t="n">
-        <v>79603</v>
+        <v>79632</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10231,21 +10231,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10255,10 +10255,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>406271</v>
+        <v>406436</v>
       </c>
       <c r="R97" t="n">
-        <v>6856003</v>
+        <v>6855599</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10317,10 +10317,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126600681</v>
+        <v>126600575</v>
       </c>
       <c r="B98" t="n">
-        <v>78681</v>
+        <v>79632</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10328,21 +10328,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10352,10 +10352,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>406422</v>
+        <v>406441</v>
       </c>
       <c r="R98" t="n">
-        <v>6856055</v>
+        <v>6855713</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10414,7 +10414,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126600541</v>
+        <v>126600563</v>
       </c>
       <c r="B99" t="n">
         <v>79632</v>
@@ -10449,10 +10449,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>406596</v>
+        <v>406460</v>
       </c>
       <c r="R99" t="n">
-        <v>6855897</v>
+        <v>6855846</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10511,7 +10511,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126600585</v>
+        <v>126600580</v>
       </c>
       <c r="B100" t="n">
         <v>79632</v>
@@ -10546,10 +10546,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>406436</v>
+        <v>406422</v>
       </c>
       <c r="R100" t="n">
-        <v>6855599</v>
+        <v>6855652</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10608,10 +10608,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126600575</v>
+        <v>126600681</v>
       </c>
       <c r="B101" t="n">
-        <v>79632</v>
+        <v>78681</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10619,21 +10619,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10643,10 +10643,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>406441</v>
+        <v>406422</v>
       </c>
       <c r="R101" t="n">
-        <v>6855713</v>
+        <v>6856055</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10705,10 +10705,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126600563</v>
+        <v>126600616</v>
       </c>
       <c r="B102" t="n">
-        <v>79632</v>
+        <v>78773</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10716,21 +10716,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10740,10 +10740,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>406460</v>
+        <v>406293</v>
       </c>
       <c r="R102" t="n">
-        <v>6855846</v>
+        <v>6855983</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10802,10 +10802,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126600580</v>
+        <v>126600589</v>
       </c>
       <c r="B103" t="n">
-        <v>79632</v>
+        <v>79603</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10813,21 +10813,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10837,10 +10837,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>406422</v>
+        <v>406271</v>
       </c>
       <c r="R103" t="n">
-        <v>6855652</v>
+        <v>6856003</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11190,10 +11190,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126600655</v>
+        <v>126600587</v>
       </c>
       <c r="B107" t="n">
-        <v>79014</v>
+        <v>75138</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11201,21 +11201,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11225,10 +11225,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>406627</v>
+        <v>406631</v>
       </c>
       <c r="R107" t="n">
-        <v>6856000</v>
+        <v>6855979</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11287,10 +11287,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126600587</v>
+        <v>126600557</v>
       </c>
       <c r="B108" t="n">
-        <v>75138</v>
+        <v>79632</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11298,21 +11298,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11322,10 +11322,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>406631</v>
+        <v>406381</v>
       </c>
       <c r="R108" t="n">
-        <v>6855979</v>
+        <v>6856048</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11384,10 +11384,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126600557</v>
+        <v>126600655</v>
       </c>
       <c r="B109" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11395,21 +11395,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11419,10 +11419,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>406381</v>
+        <v>406627</v>
       </c>
       <c r="R109" t="n">
-        <v>6856048</v>
+        <v>6856000</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11481,32 +11481,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126600606</v>
+        <v>126600573</v>
       </c>
       <c r="B110" t="n">
-        <v>97320</v>
+        <v>79632</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11516,10 +11516,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>406618</v>
+        <v>406409</v>
       </c>
       <c r="R110" t="n">
-        <v>6856011</v>
+        <v>6855915</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11578,10 +11578,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126600617</v>
+        <v>126600570</v>
       </c>
       <c r="B111" t="n">
-        <v>78773</v>
+        <v>79632</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11589,21 +11589,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11613,10 +11613,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>406303</v>
+        <v>406442</v>
       </c>
       <c r="R111" t="n">
-        <v>6855965</v>
+        <v>6855938</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11675,7 +11675,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126600573</v>
+        <v>126600542</v>
       </c>
       <c r="B112" t="n">
         <v>79632</v>
@@ -11710,10 +11710,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>406409</v>
+        <v>406587</v>
       </c>
       <c r="R112" t="n">
-        <v>6855915</v>
+        <v>6855895</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11772,10 +11772,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126600570</v>
+        <v>126600651</v>
       </c>
       <c r="B113" t="n">
-        <v>79632</v>
+        <v>91343</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11783,21 +11783,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6453</v>
+        <v>5432</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11807,10 +11807,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>406442</v>
+        <v>406515</v>
       </c>
       <c r="R113" t="n">
-        <v>6855938</v>
+        <v>6856173</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11869,7 +11869,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126600651</v>
+        <v>126600650</v>
       </c>
       <c r="B114" t="n">
         <v>91343</v>
@@ -11904,10 +11904,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>406515</v>
+        <v>406523</v>
       </c>
       <c r="R114" t="n">
-        <v>6856173</v>
+        <v>6856161</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11966,10 +11966,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126600650</v>
+        <v>126600617</v>
       </c>
       <c r="B115" t="n">
-        <v>91343</v>
+        <v>78773</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11977,21 +11977,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5432</v>
+        <v>228912</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12001,10 +12001,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>406523</v>
+        <v>406303</v>
       </c>
       <c r="R115" t="n">
-        <v>6856161</v>
+        <v>6855965</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12063,10 +12063,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126600542</v>
+        <v>126600605</v>
       </c>
       <c r="B116" t="n">
-        <v>79632</v>
+        <v>57657</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12074,34 +12074,39 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Öjvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>406587</v>
+        <v>406627</v>
       </c>
       <c r="R116" t="n">
-        <v>6855895</v>
+        <v>6856015</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12134,6 +12139,11 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12160,50 +12170,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126600605</v>
+        <v>126600606</v>
       </c>
       <c r="B117" t="n">
-        <v>57657</v>
+        <v>97320</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Öjvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>406627</v>
+        <v>406618</v>
       </c>
       <c r="R117" t="n">
-        <v>6856015</v>
+        <v>6856011</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12236,11 +12241,6 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-07-11</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12267,10 +12267,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126600658</v>
+        <v>126600549</v>
       </c>
       <c r="B118" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12278,21 +12278,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12302,10 +12302,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>406516</v>
+        <v>406306</v>
       </c>
       <c r="R118" t="n">
-        <v>6856152</v>
+        <v>6855951</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12364,10 +12364,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126600549</v>
+        <v>126600658</v>
       </c>
       <c r="B119" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12375,21 +12375,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12399,10 +12399,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>406306</v>
+        <v>406516</v>
       </c>
       <c r="R119" t="n">
-        <v>6855951</v>
+        <v>6856152</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12655,32 +12655,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126600642</v>
+        <v>126600675</v>
       </c>
       <c r="B122" t="n">
-        <v>78772</v>
+        <v>92615</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12690,10 +12690,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>406485</v>
+        <v>406442</v>
       </c>
       <c r="R122" t="n">
-        <v>6855875</v>
+        <v>6855951</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12752,10 +12752,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126600632</v>
+        <v>126600665</v>
       </c>
       <c r="B123" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12763,21 +12763,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12787,10 +12787,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>406502</v>
+        <v>406499</v>
       </c>
       <c r="R123" t="n">
-        <v>6855622</v>
+        <v>6856166</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12849,32 +12849,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126600675</v>
+        <v>126600642</v>
       </c>
       <c r="B124" t="n">
-        <v>92615</v>
+        <v>78772</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12884,10 +12884,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>406442</v>
+        <v>406485</v>
       </c>
       <c r="R124" t="n">
-        <v>6855951</v>
+        <v>6855875</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12946,10 +12946,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126600535</v>
+        <v>126600632</v>
       </c>
       <c r="B125" t="n">
-        <v>79632</v>
+        <v>78772</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12957,21 +12957,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13043,10 +13043,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126600665</v>
+        <v>126600535</v>
       </c>
       <c r="B126" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13054,21 +13054,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13078,10 +13078,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>406499</v>
+        <v>406502</v>
       </c>
       <c r="R126" t="n">
-        <v>6856166</v>
+        <v>6855622</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13334,32 +13334,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126600672</v>
+        <v>126600568</v>
       </c>
       <c r="B129" t="n">
-        <v>92615</v>
+        <v>79632</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13369,10 +13369,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>406273</v>
+        <v>406466</v>
       </c>
       <c r="R129" t="n">
-        <v>6856005</v>
+        <v>6855904</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13431,7 +13431,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126600568</v>
+        <v>126600538</v>
       </c>
       <c r="B130" t="n">
         <v>79632</v>
@@ -13466,10 +13466,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>406466</v>
+        <v>406578</v>
       </c>
       <c r="R130" t="n">
-        <v>6855904</v>
+        <v>6855748</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13528,32 +13528,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126600538</v>
+        <v>126600672</v>
       </c>
       <c r="B131" t="n">
-        <v>79632</v>
+        <v>92615</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13563,10 +13563,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>406578</v>
+        <v>406273</v>
       </c>
       <c r="R131" t="n">
-        <v>6855748</v>
+        <v>6856005</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13722,10 +13722,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126600594</v>
+        <v>126600638</v>
       </c>
       <c r="B133" t="n">
-        <v>57817</v>
+        <v>78772</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13733,21 +13733,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13757,10 +13757,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>406325</v>
+        <v>406379</v>
       </c>
       <c r="R133" t="n">
-        <v>6855978</v>
+        <v>6856040</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13819,32 +13819,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126600676</v>
+        <v>126600566</v>
       </c>
       <c r="B134" t="n">
-        <v>92615</v>
+        <v>79632</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13854,10 +13854,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>406414</v>
+        <v>406482</v>
       </c>
       <c r="R134" t="n">
-        <v>6855915</v>
+        <v>6855876</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13916,10 +13916,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126600638</v>
+        <v>126600536</v>
       </c>
       <c r="B135" t="n">
-        <v>78772</v>
+        <v>79632</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13927,21 +13927,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -13951,10 +13951,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>406379</v>
+        <v>406521</v>
       </c>
       <c r="R135" t="n">
-        <v>6856040</v>
+        <v>6855634</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14013,32 +14013,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126600566</v>
+        <v>126600676</v>
       </c>
       <c r="B136" t="n">
-        <v>79632</v>
+        <v>92615</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14048,10 +14048,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>406482</v>
+        <v>406414</v>
       </c>
       <c r="R136" t="n">
-        <v>6855876</v>
+        <v>6855915</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14110,10 +14110,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126600536</v>
+        <v>126600594</v>
       </c>
       <c r="B137" t="n">
-        <v>79632</v>
+        <v>57817</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14121,21 +14121,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14145,10 +14145,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>406521</v>
+        <v>406325</v>
       </c>
       <c r="R137" t="n">
-        <v>6855634</v>
+        <v>6855978</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14498,10 +14498,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126600667</v>
+        <v>126600547</v>
       </c>
       <c r="B141" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14509,21 +14509,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14533,10 +14533,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>406426</v>
+        <v>406285</v>
       </c>
       <c r="R141" t="n">
-        <v>6855972</v>
+        <v>6856129</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14595,32 +14595,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126600547</v>
+        <v>126600607</v>
       </c>
       <c r="B142" t="n">
-        <v>79632</v>
+        <v>97320</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6453</v>
+        <v>221945</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14630,10 +14630,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>406285</v>
+        <v>406576</v>
       </c>
       <c r="R142" t="n">
-        <v>6856129</v>
+        <v>6856013</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14692,32 +14692,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>126600607</v>
+        <v>126600667</v>
       </c>
       <c r="B143" t="n">
-        <v>97320</v>
+        <v>79014</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14727,10 +14727,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>406576</v>
+        <v>406426</v>
       </c>
       <c r="R143" t="n">
-        <v>6856013</v>
+        <v>6855972</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>

--- a/artfynd/A 29779-2025 artfynd.xlsx
+++ b/artfynd/A 29779-2025 artfynd.xlsx
@@ -4002,10 +4002,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126600635</v>
+        <v>126600556</v>
       </c>
       <c r="B33" t="n">
-        <v>78772</v>
+        <v>79632</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4013,21 +4013,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4037,10 +4037,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>406535</v>
+        <v>406389</v>
       </c>
       <c r="R33" t="n">
-        <v>6855969</v>
+        <v>6856021</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4099,10 +4099,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126600556</v>
+        <v>126600679</v>
       </c>
       <c r="B34" t="n">
-        <v>79632</v>
+        <v>78681</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4110,21 +4110,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>406389</v>
+        <v>406407</v>
       </c>
       <c r="R34" t="n">
-        <v>6856021</v>
+        <v>6856127</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4196,10 +4196,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126600679</v>
+        <v>126600620</v>
       </c>
       <c r="B35" t="n">
-        <v>78681</v>
+        <v>78773</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4207,21 +4207,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4231,10 +4231,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>406407</v>
+        <v>406376</v>
       </c>
       <c r="R35" t="n">
-        <v>6856127</v>
+        <v>6856016</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4293,10 +4293,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126600677</v>
+        <v>126600608</v>
       </c>
       <c r="B36" t="n">
-        <v>92615</v>
+        <v>97326</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4304,21 +4304,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4328,10 +4328,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>406409</v>
+        <v>406378</v>
       </c>
       <c r="R36" t="n">
-        <v>6855908</v>
+        <v>6856046</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4390,10 +4390,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126600620</v>
+        <v>126600635</v>
       </c>
       <c r="B37" t="n">
-        <v>78773</v>
+        <v>78772</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4401,21 +4401,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>406376</v>
+        <v>406535</v>
       </c>
       <c r="R37" t="n">
-        <v>6856016</v>
+        <v>6855969</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4487,10 +4487,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126600608</v>
+        <v>126600677</v>
       </c>
       <c r="B38" t="n">
-        <v>97326</v>
+        <v>92615</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4498,21 +4498,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4522,10 +4522,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>406378</v>
+        <v>406409</v>
       </c>
       <c r="R38" t="n">
-        <v>6856046</v>
+        <v>6855908</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5166,10 +5166,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126600656</v>
+        <v>126600619</v>
       </c>
       <c r="B45" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5177,21 +5177,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5201,10 +5201,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>406626</v>
+        <v>406365</v>
       </c>
       <c r="R45" t="n">
-        <v>6856024</v>
+        <v>6856013</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5554,7 +5554,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126600572</v>
+        <v>126600576</v>
       </c>
       <c r="B49" t="n">
         <v>79632</v>
@@ -5589,10 +5589,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>406428</v>
+        <v>406439</v>
       </c>
       <c r="R49" t="n">
-        <v>6855941</v>
+        <v>6855706</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5651,10 +5651,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126600576</v>
+        <v>126600656</v>
       </c>
       <c r="B50" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5662,21 +5662,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5686,10 +5686,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>406439</v>
+        <v>406626</v>
       </c>
       <c r="R50" t="n">
-        <v>6855706</v>
+        <v>6856024</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5748,10 +5748,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126600619</v>
+        <v>126600572</v>
       </c>
       <c r="B51" t="n">
-        <v>78773</v>
+        <v>79632</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5759,21 +5759,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5783,10 +5783,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>406365</v>
+        <v>406428</v>
       </c>
       <c r="R51" t="n">
-        <v>6856013</v>
+        <v>6855941</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6330,10 +6330,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126600663</v>
+        <v>126600645</v>
       </c>
       <c r="B57" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6341,21 +6341,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6365,10 +6365,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>406523</v>
+        <v>406440</v>
       </c>
       <c r="R57" t="n">
-        <v>6856176</v>
+        <v>6855714</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6427,32 +6427,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126600645</v>
+        <v>126600601</v>
       </c>
       <c r="B58" t="n">
-        <v>78772</v>
+        <v>98463</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>221952</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6462,10 +6462,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>406440</v>
+        <v>406524</v>
       </c>
       <c r="R58" t="n">
-        <v>6855714</v>
+        <v>6856188</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6524,10 +6524,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126600590</v>
+        <v>126600663</v>
       </c>
       <c r="B59" t="n">
-        <v>79603</v>
+        <v>79014</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6535,21 +6535,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6559,10 +6559,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>406293</v>
+        <v>406523</v>
       </c>
       <c r="R59" t="n">
-        <v>6855983</v>
+        <v>6856176</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6621,32 +6621,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126600601</v>
+        <v>126600590</v>
       </c>
       <c r="B60" t="n">
-        <v>98463</v>
+        <v>79603</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221952</v>
+        <v>229821</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6656,10 +6656,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>406524</v>
+        <v>406293</v>
       </c>
       <c r="R60" t="n">
-        <v>6856188</v>
+        <v>6855983</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8954,7 +8954,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126600560</v>
+        <v>126600546</v>
       </c>
       <c r="B84" t="n">
         <v>79632</v>
@@ -8989,10 +8989,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>406434</v>
+        <v>406343</v>
       </c>
       <c r="R84" t="n">
-        <v>6856017</v>
+        <v>6856059</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9051,10 +9051,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126600546</v>
+        <v>126600678</v>
       </c>
       <c r="B85" t="n">
-        <v>79632</v>
+        <v>78681</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9062,21 +9062,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9086,10 +9086,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>406343</v>
+        <v>406585</v>
       </c>
       <c r="R85" t="n">
-        <v>6856059</v>
+        <v>6856016</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9148,10 +9148,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126600678</v>
+        <v>126600560</v>
       </c>
       <c r="B86" t="n">
-        <v>78681</v>
+        <v>79632</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9159,21 +9159,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9183,10 +9183,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>406585</v>
+        <v>406434</v>
       </c>
       <c r="R86" t="n">
-        <v>6856016</v>
+        <v>6856017</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9541,32 +9541,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126600628</v>
+        <v>126600591</v>
       </c>
       <c r="B90" t="n">
-        <v>78773</v>
+        <v>91290</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>228912</v>
+        <v>5447</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9576,10 +9576,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>406471</v>
+        <v>406266</v>
       </c>
       <c r="R90" t="n">
-        <v>6855896</v>
+        <v>6856149</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9638,10 +9638,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126600630</v>
+        <v>126600611</v>
       </c>
       <c r="B91" t="n">
-        <v>78773</v>
+        <v>92808</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9649,21 +9649,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9673,10 +9673,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>406428</v>
+        <v>406433</v>
       </c>
       <c r="R91" t="n">
-        <v>6855941</v>
+        <v>6855894</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9735,32 +9735,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126600591</v>
+        <v>126600660</v>
       </c>
       <c r="B92" t="n">
-        <v>91290</v>
+        <v>79014</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9770,10 +9770,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>406266</v>
+        <v>406521</v>
       </c>
       <c r="R92" t="n">
-        <v>6856149</v>
+        <v>6856195</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9832,10 +9832,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126600611</v>
+        <v>126600657</v>
       </c>
       <c r="B93" t="n">
-        <v>92808</v>
+        <v>79014</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9843,21 +9843,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9867,10 +9867,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>406433</v>
+        <v>406513</v>
       </c>
       <c r="R93" t="n">
-        <v>6855894</v>
+        <v>6856139</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9929,10 +9929,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126600660</v>
+        <v>126600628</v>
       </c>
       <c r="B94" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9940,21 +9940,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9964,10 +9964,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>406521</v>
+        <v>406471</v>
       </c>
       <c r="R94" t="n">
-        <v>6856195</v>
+        <v>6855896</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10026,10 +10026,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126600657</v>
+        <v>126600630</v>
       </c>
       <c r="B95" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10037,21 +10037,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10061,10 +10061,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>406513</v>
+        <v>406428</v>
       </c>
       <c r="R95" t="n">
-        <v>6856139</v>
+        <v>6855941</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11481,10 +11481,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126600573</v>
+        <v>126600605</v>
       </c>
       <c r="B110" t="n">
-        <v>79632</v>
+        <v>57657</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11492,34 +11492,39 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Öjvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>406409</v>
+        <v>406627</v>
       </c>
       <c r="R110" t="n">
-        <v>6855915</v>
+        <v>6856015</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11552,6 +11557,11 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11578,7 +11588,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126600570</v>
+        <v>126600573</v>
       </c>
       <c r="B111" t="n">
         <v>79632</v>
@@ -11613,10 +11623,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>406442</v>
+        <v>406409</v>
       </c>
       <c r="R111" t="n">
-        <v>6855938</v>
+        <v>6855915</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11675,7 +11685,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126600542</v>
+        <v>126600570</v>
       </c>
       <c r="B112" t="n">
         <v>79632</v>
@@ -11710,10 +11720,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>406587</v>
+        <v>406442</v>
       </c>
       <c r="R112" t="n">
-        <v>6855895</v>
+        <v>6855938</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11772,10 +11782,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126600651</v>
+        <v>126600542</v>
       </c>
       <c r="B113" t="n">
-        <v>91343</v>
+        <v>79632</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11783,21 +11793,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11807,10 +11817,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>406515</v>
+        <v>406587</v>
       </c>
       <c r="R113" t="n">
-        <v>6856173</v>
+        <v>6855895</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11869,7 +11879,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126600650</v>
+        <v>126600651</v>
       </c>
       <c r="B114" t="n">
         <v>91343</v>
@@ -11904,10 +11914,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>406523</v>
+        <v>406515</v>
       </c>
       <c r="R114" t="n">
-        <v>6856161</v>
+        <v>6856173</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11966,10 +11976,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126600617</v>
+        <v>126600650</v>
       </c>
       <c r="B115" t="n">
-        <v>78773</v>
+        <v>91343</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11977,21 +11987,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>228912</v>
+        <v>5432</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12001,10 +12011,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>406303</v>
+        <v>406523</v>
       </c>
       <c r="R115" t="n">
-        <v>6855965</v>
+        <v>6856161</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12063,10 +12073,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126600605</v>
+        <v>126600617</v>
       </c>
       <c r="B116" t="n">
-        <v>57657</v>
+        <v>78773</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12074,39 +12084,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Öjvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>406627</v>
+        <v>406303</v>
       </c>
       <c r="R116" t="n">
-        <v>6856015</v>
+        <v>6855965</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12139,11 +12144,6 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-07-11</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13334,10 +13334,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126600568</v>
+        <v>126600625</v>
       </c>
       <c r="B129" t="n">
-        <v>79632</v>
+        <v>78773</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13345,21 +13345,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13369,10 +13369,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>406466</v>
+        <v>406434</v>
       </c>
       <c r="R129" t="n">
-        <v>6855904</v>
+        <v>6856017</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13431,7 +13431,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126600538</v>
+        <v>126600568</v>
       </c>
       <c r="B130" t="n">
         <v>79632</v>
@@ -13466,10 +13466,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>406578</v>
+        <v>406466</v>
       </c>
       <c r="R130" t="n">
-        <v>6855748</v>
+        <v>6855904</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13528,32 +13528,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126600672</v>
+        <v>126600538</v>
       </c>
       <c r="B131" t="n">
-        <v>92615</v>
+        <v>79632</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13563,10 +13563,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>406273</v>
+        <v>406578</v>
       </c>
       <c r="R131" t="n">
-        <v>6856005</v>
+        <v>6855748</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13625,32 +13625,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126600625</v>
+        <v>126600672</v>
       </c>
       <c r="B132" t="n">
-        <v>78773</v>
+        <v>92615</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13660,10 +13660,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>406434</v>
+        <v>406273</v>
       </c>
       <c r="R132" t="n">
-        <v>6856017</v>
+        <v>6856005</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>

--- a/artfynd/A 29779-2025 artfynd.xlsx
+++ b/artfynd/A 29779-2025 artfynd.xlsx
@@ -3031,7 +3031,7 @@
         <v>126600584</v>
       </c>
       <c r="B23" t="n">
-        <v>79632</v>
+        <v>79629</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3125,10 +3125,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126600545</v>
+        <v>126600666</v>
       </c>
       <c r="B24" t="n">
-        <v>79632</v>
+        <v>79011</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3136,21 +3136,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3160,10 +3160,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>406516</v>
+        <v>406495</v>
       </c>
       <c r="R24" t="n">
-        <v>6856086</v>
+        <v>6856163</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3222,10 +3222,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126600688</v>
+        <v>126600545</v>
       </c>
       <c r="B25" t="n">
-        <v>78420</v>
+        <v>79629</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3233,21 +3233,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3257,10 +3257,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>406442</v>
+        <v>406516</v>
       </c>
       <c r="R25" t="n">
-        <v>6855707</v>
+        <v>6856086</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3319,10 +3319,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126600666</v>
+        <v>126600688</v>
       </c>
       <c r="B26" t="n">
-        <v>79014</v>
+        <v>78417</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3330,21 +3330,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3354,10 +3354,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>406495</v>
+        <v>406442</v>
       </c>
       <c r="R26" t="n">
-        <v>6856163</v>
+        <v>6855707</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3419,7 +3419,7 @@
         <v>126600668</v>
       </c>
       <c r="B27" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3513,10 +3513,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126600621</v>
+        <v>126600593</v>
       </c>
       <c r="B28" t="n">
-        <v>78773</v>
+        <v>57817</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3524,34 +3524,38 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Öjvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>406382</v>
+        <v>406292</v>
       </c>
       <c r="R28" t="n">
-        <v>6856055</v>
+        <v>6856034</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3610,10 +3614,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126600593</v>
+        <v>126600621</v>
       </c>
       <c r="B29" t="n">
-        <v>57817</v>
+        <v>78770</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3621,38 +3625,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Öjvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>406292</v>
+        <v>406382</v>
       </c>
       <c r="R29" t="n">
-        <v>6856034</v>
+        <v>6856055</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3714,7 +3714,7 @@
         <v>126600627</v>
       </c>
       <c r="B30" t="n">
-        <v>78773</v>
+        <v>78770</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>126600623</v>
       </c>
       <c r="B31" t="n">
-        <v>78773</v>
+        <v>78770</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3905,32 +3905,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126600639</v>
+        <v>126600608</v>
       </c>
       <c r="B32" t="n">
-        <v>78772</v>
+        <v>97320</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>221941</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3940,10 +3940,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>406433</v>
+        <v>406378</v>
       </c>
       <c r="R32" t="n">
-        <v>6856017</v>
+        <v>6856046</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4002,10 +4002,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126600556</v>
+        <v>126600620</v>
       </c>
       <c r="B33" t="n">
-        <v>79632</v>
+        <v>78770</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4013,21 +4013,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4037,10 +4037,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>406389</v>
+        <v>406376</v>
       </c>
       <c r="R33" t="n">
-        <v>6856021</v>
+        <v>6856016</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4099,10 +4099,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126600679</v>
+        <v>126600639</v>
       </c>
       <c r="B34" t="n">
-        <v>78681</v>
+        <v>78769</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4110,21 +4110,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>406407</v>
+        <v>406433</v>
       </c>
       <c r="R34" t="n">
-        <v>6856127</v>
+        <v>6856017</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4196,10 +4196,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126600620</v>
+        <v>126600635</v>
       </c>
       <c r="B35" t="n">
-        <v>78773</v>
+        <v>78769</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4207,21 +4207,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4231,10 +4231,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>406376</v>
+        <v>406535</v>
       </c>
       <c r="R35" t="n">
-        <v>6856016</v>
+        <v>6855969</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4293,32 +4293,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126600608</v>
+        <v>126600556</v>
       </c>
       <c r="B36" t="n">
-        <v>97326</v>
+        <v>79629</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4328,10 +4328,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>406378</v>
+        <v>406389</v>
       </c>
       <c r="R36" t="n">
-        <v>6856046</v>
+        <v>6856021</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4390,10 +4390,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126600635</v>
+        <v>126600679</v>
       </c>
       <c r="B37" t="n">
-        <v>78772</v>
+        <v>78678</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4401,21 +4401,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>406535</v>
+        <v>406407</v>
       </c>
       <c r="R37" t="n">
-        <v>6855969</v>
+        <v>6856127</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4490,7 +4490,7 @@
         <v>126600677</v>
       </c>
       <c r="B38" t="n">
-        <v>92615</v>
+        <v>92609</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         <v>126600561</v>
       </c>
       <c r="B39" t="n">
-        <v>79632</v>
+        <v>79629</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4684,7 +4684,7 @@
         <v>126600579</v>
       </c>
       <c r="B40" t="n">
-        <v>79632</v>
+        <v>79629</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>126600553</v>
       </c>
       <c r="B41" t="n">
-        <v>79632</v>
+        <v>79629</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>126600567</v>
       </c>
       <c r="B42" t="n">
-        <v>79632</v>
+        <v>79629</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>126600626</v>
       </c>
       <c r="B43" t="n">
-        <v>78773</v>
+        <v>78770</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>126600629</v>
       </c>
       <c r="B44" t="n">
-        <v>78773</v>
+        <v>78770</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5166,10 +5166,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126600619</v>
+        <v>126600656</v>
       </c>
       <c r="B45" t="n">
-        <v>78773</v>
+        <v>79011</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5177,21 +5177,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5201,10 +5201,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>406365</v>
+        <v>406626</v>
       </c>
       <c r="R45" t="n">
-        <v>6856013</v>
+        <v>6856024</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5266,7 +5266,7 @@
         <v>126600548</v>
       </c>
       <c r="B46" t="n">
-        <v>79632</v>
+        <v>79629</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5363,7 +5363,7 @@
         <v>126600559</v>
       </c>
       <c r="B47" t="n">
-        <v>79632</v>
+        <v>79629</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         <v>126600582</v>
       </c>
       <c r="B48" t="n">
-        <v>79632</v>
+        <v>79629</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5554,10 +5554,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126600576</v>
+        <v>126600572</v>
       </c>
       <c r="B49" t="n">
-        <v>79632</v>
+        <v>79629</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5589,10 +5589,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>406439</v>
+        <v>406428</v>
       </c>
       <c r="R49" t="n">
-        <v>6855706</v>
+        <v>6855941</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5651,10 +5651,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126600656</v>
+        <v>126600576</v>
       </c>
       <c r="B50" t="n">
-        <v>79014</v>
+        <v>79629</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5662,21 +5662,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5686,10 +5686,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>406626</v>
+        <v>406439</v>
       </c>
       <c r="R50" t="n">
-        <v>6856024</v>
+        <v>6855706</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5748,10 +5748,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126600572</v>
+        <v>126600619</v>
       </c>
       <c r="B51" t="n">
-        <v>79632</v>
+        <v>78770</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5759,21 +5759,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5783,10 +5783,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>406428</v>
+        <v>406365</v>
       </c>
       <c r="R51" t="n">
-        <v>6855941</v>
+        <v>6856013</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5845,10 +5845,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126600586</v>
+        <v>126600554</v>
       </c>
       <c r="B52" t="n">
-        <v>91247</v>
+        <v>79629</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5856,21 +5856,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3242</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5880,10 +5880,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>406331</v>
+        <v>406376</v>
       </c>
       <c r="R52" t="n">
-        <v>6855997</v>
+        <v>6856016</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5942,10 +5942,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126600618</v>
+        <v>126600558</v>
       </c>
       <c r="B53" t="n">
-        <v>78773</v>
+        <v>79629</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5953,21 +5953,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5977,10 +5977,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>406323</v>
+        <v>406382</v>
       </c>
       <c r="R53" t="n">
-        <v>6856001</v>
+        <v>6856055</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6039,10 +6039,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126600554</v>
+        <v>126600643</v>
       </c>
       <c r="B54" t="n">
-        <v>79632</v>
+        <v>78769</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6050,21 +6050,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6074,10 +6074,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>406376</v>
+        <v>406462</v>
       </c>
       <c r="R54" t="n">
-        <v>6856016</v>
+        <v>6855914</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6136,10 +6136,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126600558</v>
+        <v>126600618</v>
       </c>
       <c r="B55" t="n">
-        <v>79632</v>
+        <v>78770</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6147,21 +6147,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6171,10 +6171,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>406382</v>
+        <v>406323</v>
       </c>
       <c r="R55" t="n">
-        <v>6856055</v>
+        <v>6856001</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6233,10 +6233,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126600643</v>
+        <v>126600586</v>
       </c>
       <c r="B56" t="n">
-        <v>78772</v>
+        <v>91241</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6244,21 +6244,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>3242</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6268,10 +6268,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>406462</v>
+        <v>406331</v>
       </c>
       <c r="R56" t="n">
-        <v>6855914</v>
+        <v>6855997</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6330,10 +6330,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126600645</v>
+        <v>126600663</v>
       </c>
       <c r="B57" t="n">
-        <v>78772</v>
+        <v>79011</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6341,21 +6341,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6365,10 +6365,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>406440</v>
+        <v>406523</v>
       </c>
       <c r="R57" t="n">
-        <v>6855714</v>
+        <v>6856176</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6427,32 +6427,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126600601</v>
+        <v>126600645</v>
       </c>
       <c r="B58" t="n">
-        <v>98463</v>
+        <v>78769</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221952</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6462,10 +6462,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>406524</v>
+        <v>406440</v>
       </c>
       <c r="R58" t="n">
-        <v>6856188</v>
+        <v>6855714</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6524,32 +6524,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126600663</v>
+        <v>126600601</v>
       </c>
       <c r="B59" t="n">
-        <v>79014</v>
+        <v>98457</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6559,10 +6559,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>406523</v>
+        <v>406524</v>
       </c>
       <c r="R59" t="n">
-        <v>6856176</v>
+        <v>6856188</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6624,7 +6624,7 @@
         <v>126600590</v>
       </c>
       <c r="B60" t="n">
-        <v>79603</v>
+        <v>79600</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         <v>126600653</v>
       </c>
       <c r="B61" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6815,10 +6815,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126600654</v>
+        <v>126600636</v>
       </c>
       <c r="B62" t="n">
-        <v>79014</v>
+        <v>78769</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6826,21 +6826,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6850,10 +6850,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>406623</v>
+        <v>406307</v>
       </c>
       <c r="R62" t="n">
-        <v>6855990</v>
+        <v>6855949</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6912,10 +6912,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126600614</v>
+        <v>126600565</v>
       </c>
       <c r="B63" t="n">
-        <v>78773</v>
+        <v>79629</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6923,21 +6923,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6947,10 +6947,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>406294</v>
+        <v>406485</v>
       </c>
       <c r="R63" t="n">
-        <v>6856039</v>
+        <v>6855873</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7009,10 +7009,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126600636</v>
+        <v>126600684</v>
       </c>
       <c r="B64" t="n">
-        <v>78772</v>
+        <v>78417</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7020,21 +7020,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7044,10 +7044,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>406307</v>
+        <v>406294</v>
       </c>
       <c r="R64" t="n">
-        <v>6855949</v>
+        <v>6855983</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7106,10 +7106,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126600565</v>
+        <v>126600654</v>
       </c>
       <c r="B65" t="n">
-        <v>79632</v>
+        <v>79011</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7117,21 +7117,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7141,10 +7141,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>406485</v>
+        <v>406623</v>
       </c>
       <c r="R65" t="n">
-        <v>6855873</v>
+        <v>6855990</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7203,10 +7203,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126600684</v>
+        <v>126600614</v>
       </c>
       <c r="B66" t="n">
-        <v>78420</v>
+        <v>78770</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7214,21 +7214,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7241,7 +7241,7 @@
         <v>406294</v>
       </c>
       <c r="R66" t="n">
-        <v>6855983</v>
+        <v>6856039</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7300,10 +7300,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126600624</v>
+        <v>126600644</v>
       </c>
       <c r="B67" t="n">
-        <v>78773</v>
+        <v>78769</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7311,21 +7311,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7335,10 +7335,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>406429</v>
+        <v>406406</v>
       </c>
       <c r="R67" t="n">
-        <v>6856032</v>
+        <v>6855855</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7397,10 +7397,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126600613</v>
+        <v>126600664</v>
       </c>
       <c r="B68" t="n">
-        <v>78773</v>
+        <v>79011</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7408,21 +7408,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7432,10 +7432,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>406469</v>
+        <v>406512</v>
       </c>
       <c r="R68" t="n">
-        <v>6855892</v>
+        <v>6856169</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7468,11 +7468,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-07-11</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>På stubbe med 3 brandljud</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7499,10 +7494,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126600664</v>
+        <v>126600683</v>
       </c>
       <c r="B69" t="n">
-        <v>79014</v>
+        <v>78417</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7510,21 +7505,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7534,10 +7529,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>406512</v>
+        <v>406500</v>
       </c>
       <c r="R69" t="n">
-        <v>6856169</v>
+        <v>6856028</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7596,10 +7591,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126600644</v>
+        <v>126600624</v>
       </c>
       <c r="B70" t="n">
-        <v>78772</v>
+        <v>78770</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7607,21 +7602,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7631,10 +7626,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>406406</v>
+        <v>406429</v>
       </c>
       <c r="R70" t="n">
-        <v>6855855</v>
+        <v>6856032</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7693,10 +7688,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126600683</v>
+        <v>126600613</v>
       </c>
       <c r="B71" t="n">
-        <v>78420</v>
+        <v>78770</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7704,21 +7699,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7728,10 +7723,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>406500</v>
+        <v>406469</v>
       </c>
       <c r="R71" t="n">
-        <v>6856028</v>
+        <v>6855892</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7764,6 +7759,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>På stubbe med 3 brandljud</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7793,7 +7793,7 @@
         <v>126600551</v>
       </c>
       <c r="B72" t="n">
-        <v>79632</v>
+        <v>79629</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>126600555</v>
       </c>
       <c r="B73" t="n">
-        <v>79632</v>
+        <v>79629</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7987,7 +7987,7 @@
         <v>126600569</v>
       </c>
       <c r="B74" t="n">
-        <v>79632</v>
+        <v>79629</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
         <v>126600640</v>
       </c>
       <c r="B75" t="n">
-        <v>78772</v>
+        <v>78769</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8181,7 +8181,7 @@
         <v>126600552</v>
       </c>
       <c r="B76" t="n">
-        <v>79632</v>
+        <v>79629</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>126600537</v>
       </c>
       <c r="B77" t="n">
-        <v>79632</v>
+        <v>79629</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>126600631</v>
       </c>
       <c r="B78" t="n">
-        <v>80989</v>
+        <v>80986</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8469,10 +8469,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126600615</v>
+        <v>126600581</v>
       </c>
       <c r="B79" t="n">
-        <v>78773</v>
+        <v>79629</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8480,21 +8480,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8504,10 +8504,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>406271</v>
+        <v>406418</v>
       </c>
       <c r="R79" t="n">
-        <v>6856003</v>
+        <v>6855644</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8566,10 +8566,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126600581</v>
+        <v>126600571</v>
       </c>
       <c r="B80" t="n">
-        <v>79632</v>
+        <v>79629</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8601,10 +8601,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>406418</v>
+        <v>406431</v>
       </c>
       <c r="R80" t="n">
-        <v>6855644</v>
+        <v>6855941</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8666,7 +8666,7 @@
         <v>126600680</v>
       </c>
       <c r="B81" t="n">
-        <v>78681</v>
+        <v>78678</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8760,10 +8760,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126600571</v>
+        <v>126600615</v>
       </c>
       <c r="B82" t="n">
-        <v>79632</v>
+        <v>78770</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8771,21 +8771,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8795,10 +8795,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>406431</v>
+        <v>406271</v>
       </c>
       <c r="R82" t="n">
-        <v>6855941</v>
+        <v>6856003</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8857,10 +8857,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126600544</v>
+        <v>126600652</v>
       </c>
       <c r="B83" t="n">
-        <v>79632</v>
+        <v>79011</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8868,21 +8868,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8892,10 +8892,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>406538</v>
+        <v>406459</v>
       </c>
       <c r="R83" t="n">
-        <v>6855980</v>
+        <v>6855873</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8928,6 +8928,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>På gammeltall utan hänsynsmarkering</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8954,10 +8959,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126600546</v>
+        <v>126600544</v>
       </c>
       <c r="B84" t="n">
-        <v>79632</v>
+        <v>79629</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8989,10 +8994,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>406343</v>
+        <v>406538</v>
       </c>
       <c r="R84" t="n">
-        <v>6856059</v>
+        <v>6855980</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9051,10 +9056,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126600678</v>
+        <v>126600560</v>
       </c>
       <c r="B85" t="n">
-        <v>78681</v>
+        <v>79629</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9062,21 +9067,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9086,10 +9091,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>406585</v>
+        <v>406434</v>
       </c>
       <c r="R85" t="n">
-        <v>6856016</v>
+        <v>6856017</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9148,10 +9153,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126600560</v>
+        <v>126600546</v>
       </c>
       <c r="B86" t="n">
-        <v>79632</v>
+        <v>79629</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9183,10 +9188,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>406434</v>
+        <v>406343</v>
       </c>
       <c r="R86" t="n">
-        <v>6856017</v>
+        <v>6856059</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9245,10 +9250,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126600652</v>
+        <v>126600678</v>
       </c>
       <c r="B87" t="n">
-        <v>79014</v>
+        <v>78678</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9256,21 +9261,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9280,10 +9285,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>406459</v>
+        <v>406585</v>
       </c>
       <c r="R87" t="n">
-        <v>6855873</v>
+        <v>6856016</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9316,11 +9321,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-07-11</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>På gammeltall utan hänsynsmarkering</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9350,7 +9350,7 @@
         <v>126600577</v>
       </c>
       <c r="B88" t="n">
-        <v>79632</v>
+        <v>79629</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9444,32 +9444,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126600543</v>
+        <v>126600591</v>
       </c>
       <c r="B89" t="n">
-        <v>79632</v>
+        <v>91284</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9479,10 +9479,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>406586</v>
+        <v>406266</v>
       </c>
       <c r="R89" t="n">
-        <v>6856018</v>
+        <v>6856149</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9541,32 +9541,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126600591</v>
+        <v>126600660</v>
       </c>
       <c r="B90" t="n">
-        <v>91290</v>
+        <v>79011</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9576,10 +9576,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>406266</v>
+        <v>406521</v>
       </c>
       <c r="R90" t="n">
-        <v>6856149</v>
+        <v>6856195</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9638,10 +9638,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126600611</v>
+        <v>126600657</v>
       </c>
       <c r="B91" t="n">
-        <v>92808</v>
+        <v>79011</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9649,21 +9649,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9673,10 +9673,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>406433</v>
+        <v>406513</v>
       </c>
       <c r="R91" t="n">
-        <v>6855894</v>
+        <v>6856139</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9735,10 +9735,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126600660</v>
+        <v>126600543</v>
       </c>
       <c r="B92" t="n">
-        <v>79014</v>
+        <v>79629</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9746,21 +9746,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9770,10 +9770,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>406521</v>
+        <v>406586</v>
       </c>
       <c r="R92" t="n">
-        <v>6856195</v>
+        <v>6856018</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9832,10 +9832,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126600657</v>
+        <v>126600611</v>
       </c>
       <c r="B93" t="n">
-        <v>79014</v>
+        <v>92802</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9843,21 +9843,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9867,10 +9867,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>406513</v>
+        <v>406433</v>
       </c>
       <c r="R93" t="n">
-        <v>6856139</v>
+        <v>6855894</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9932,7 +9932,7 @@
         <v>126600628</v>
       </c>
       <c r="B94" t="n">
-        <v>78773</v>
+        <v>78770</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10029,7 +10029,7 @@
         <v>126600630</v>
       </c>
       <c r="B95" t="n">
-        <v>78773</v>
+        <v>78770</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10126,7 +10126,7 @@
         <v>126600541</v>
       </c>
       <c r="B96" t="n">
-        <v>79632</v>
+        <v>79629</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10223,7 +10223,7 @@
         <v>126600585</v>
       </c>
       <c r="B97" t="n">
-        <v>79632</v>
+        <v>79629</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         <v>126600575</v>
       </c>
       <c r="B98" t="n">
-        <v>79632</v>
+        <v>79629</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10417,7 +10417,7 @@
         <v>126600563</v>
       </c>
       <c r="B99" t="n">
-        <v>79632</v>
+        <v>79629</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10514,7 +10514,7 @@
         <v>126600580</v>
       </c>
       <c r="B100" t="n">
-        <v>79632</v>
+        <v>79629</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10611,7 +10611,7 @@
         <v>126600681</v>
       </c>
       <c r="B101" t="n">
-        <v>78681</v>
+        <v>78678</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10708,7 +10708,7 @@
         <v>126600616</v>
       </c>
       <c r="B102" t="n">
-        <v>78773</v>
+        <v>78770</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10805,7 +10805,7 @@
         <v>126600589</v>
       </c>
       <c r="B103" t="n">
-        <v>79603</v>
+        <v>79600</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10902,7 +10902,7 @@
         <v>126600622</v>
       </c>
       <c r="B104" t="n">
-        <v>78773</v>
+        <v>78770</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>126600637</v>
       </c>
       <c r="B105" t="n">
-        <v>78772</v>
+        <v>78769</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11096,7 +11096,7 @@
         <v>126600574</v>
       </c>
       <c r="B106" t="n">
-        <v>79632</v>
+        <v>79629</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11190,10 +11190,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126600587</v>
+        <v>126600655</v>
       </c>
       <c r="B107" t="n">
-        <v>75138</v>
+        <v>79011</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11201,21 +11201,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11225,10 +11225,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>406631</v>
+        <v>406627</v>
       </c>
       <c r="R107" t="n">
-        <v>6855979</v>
+        <v>6856000</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11287,10 +11287,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126600557</v>
+        <v>126600587</v>
       </c>
       <c r="B108" t="n">
-        <v>79632</v>
+        <v>75135</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11298,21 +11298,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11322,10 +11322,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>406381</v>
+        <v>406631</v>
       </c>
       <c r="R108" t="n">
-        <v>6856048</v>
+        <v>6855979</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11384,10 +11384,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126600655</v>
+        <v>126600557</v>
       </c>
       <c r="B109" t="n">
-        <v>79014</v>
+        <v>79629</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11395,21 +11395,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11419,10 +11419,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>406627</v>
+        <v>406381</v>
       </c>
       <c r="R109" t="n">
-        <v>6856000</v>
+        <v>6856048</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11481,50 +11481,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126600605</v>
+        <v>126600606</v>
       </c>
       <c r="B110" t="n">
-        <v>57657</v>
+        <v>97314</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Öjvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>406627</v>
+        <v>406618</v>
       </c>
       <c r="R110" t="n">
-        <v>6856015</v>
+        <v>6856011</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11557,11 +11552,6 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-07-11</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11591,7 +11581,7 @@
         <v>126600573</v>
       </c>
       <c r="B111" t="n">
-        <v>79632</v>
+        <v>79629</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11688,7 +11678,7 @@
         <v>126600570</v>
       </c>
       <c r="B112" t="n">
-        <v>79632</v>
+        <v>79629</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11782,10 +11772,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126600542</v>
+        <v>126600651</v>
       </c>
       <c r="B113" t="n">
-        <v>79632</v>
+        <v>91337</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11793,21 +11783,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6453</v>
+        <v>5432</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11817,10 +11807,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>406587</v>
+        <v>406515</v>
       </c>
       <c r="R113" t="n">
-        <v>6855895</v>
+        <v>6856173</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11879,10 +11869,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126600651</v>
+        <v>126600650</v>
       </c>
       <c r="B114" t="n">
-        <v>91343</v>
+        <v>91337</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11914,10 +11904,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>406515</v>
+        <v>406523</v>
       </c>
       <c r="R114" t="n">
-        <v>6856173</v>
+        <v>6856161</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11976,10 +11966,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126600650</v>
+        <v>126600542</v>
       </c>
       <c r="B115" t="n">
-        <v>91343</v>
+        <v>79629</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11987,21 +11977,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12011,10 +12001,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>406523</v>
+        <v>406587</v>
       </c>
       <c r="R115" t="n">
-        <v>6856161</v>
+        <v>6855895</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12073,10 +12063,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126600617</v>
+        <v>126600605</v>
       </c>
       <c r="B116" t="n">
-        <v>78773</v>
+        <v>57657</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12084,34 +12074,39 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Öjvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>406303</v>
+        <v>406627</v>
       </c>
       <c r="R116" t="n">
-        <v>6855965</v>
+        <v>6856015</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12144,6 +12139,11 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12170,32 +12170,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126600606</v>
+        <v>126600617</v>
       </c>
       <c r="B117" t="n">
-        <v>97320</v>
+        <v>78770</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>221945</v>
+        <v>228912</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12205,10 +12205,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>406618</v>
+        <v>406303</v>
       </c>
       <c r="R117" t="n">
-        <v>6856011</v>
+        <v>6855965</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12267,10 +12267,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126600549</v>
+        <v>126600658</v>
       </c>
       <c r="B118" t="n">
-        <v>79632</v>
+        <v>79011</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12278,21 +12278,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12302,10 +12302,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>406306</v>
+        <v>406516</v>
       </c>
       <c r="R118" t="n">
-        <v>6855951</v>
+        <v>6856152</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12364,10 +12364,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126600658</v>
+        <v>126600549</v>
       </c>
       <c r="B119" t="n">
-        <v>79014</v>
+        <v>79629</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12375,21 +12375,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12399,10 +12399,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>406516</v>
+        <v>406306</v>
       </c>
       <c r="R119" t="n">
-        <v>6856152</v>
+        <v>6855951</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12464,7 +12464,7 @@
         <v>126600673</v>
       </c>
       <c r="B120" t="n">
-        <v>92615</v>
+        <v>92609</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12558,10 +12558,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126600682</v>
+        <v>126600642</v>
       </c>
       <c r="B121" t="n">
-        <v>78681</v>
+        <v>78769</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12569,21 +12569,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12593,10 +12593,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>406425</v>
+        <v>406485</v>
       </c>
       <c r="R121" t="n">
-        <v>6855965</v>
+        <v>6855875</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12655,32 +12655,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126600675</v>
+        <v>126600632</v>
       </c>
       <c r="B122" t="n">
-        <v>92615</v>
+        <v>78769</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12690,10 +12690,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>406442</v>
+        <v>406502</v>
       </c>
       <c r="R122" t="n">
-        <v>6855951</v>
+        <v>6855622</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12752,10 +12752,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126600665</v>
+        <v>126600535</v>
       </c>
       <c r="B123" t="n">
-        <v>79014</v>
+        <v>79629</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12763,21 +12763,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12787,10 +12787,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>406499</v>
+        <v>406502</v>
       </c>
       <c r="R123" t="n">
-        <v>6856166</v>
+        <v>6855622</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12849,10 +12849,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126600642</v>
+        <v>126600665</v>
       </c>
       <c r="B124" t="n">
-        <v>78772</v>
+        <v>79011</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12860,21 +12860,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12884,10 +12884,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>406485</v>
+        <v>406499</v>
       </c>
       <c r="R124" t="n">
-        <v>6855875</v>
+        <v>6856166</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12946,10 +12946,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126600632</v>
+        <v>126600634</v>
       </c>
       <c r="B125" t="n">
-        <v>78772</v>
+        <v>78769</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12981,10 +12981,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>406502</v>
+        <v>406580</v>
       </c>
       <c r="R125" t="n">
-        <v>6855622</v>
+        <v>6855911</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13043,10 +13043,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126600535</v>
+        <v>126600562</v>
       </c>
       <c r="B126" t="n">
-        <v>79632</v>
+        <v>79629</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13078,10 +13078,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>406502</v>
+        <v>406422</v>
       </c>
       <c r="R126" t="n">
-        <v>6855622</v>
+        <v>6855969</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13140,10 +13140,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126600634</v>
+        <v>126600682</v>
       </c>
       <c r="B127" t="n">
-        <v>78772</v>
+        <v>78678</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13151,21 +13151,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13175,10 +13175,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>406580</v>
+        <v>406425</v>
       </c>
       <c r="R127" t="n">
-        <v>6855911</v>
+        <v>6855965</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13237,32 +13237,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126600562</v>
+        <v>126600675</v>
       </c>
       <c r="B128" t="n">
-        <v>79632</v>
+        <v>92609</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13272,10 +13272,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>406422</v>
+        <v>406442</v>
       </c>
       <c r="R128" t="n">
-        <v>6855969</v>
+        <v>6855951</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13334,32 +13334,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126600625</v>
+        <v>126600672</v>
       </c>
       <c r="B129" t="n">
-        <v>78773</v>
+        <v>92609</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13369,10 +13369,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>406434</v>
+        <v>406273</v>
       </c>
       <c r="R129" t="n">
-        <v>6856017</v>
+        <v>6856005</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13434,7 +13434,7 @@
         <v>126600568</v>
       </c>
       <c r="B130" t="n">
-        <v>79632</v>
+        <v>79629</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13531,7 +13531,7 @@
         <v>126600538</v>
       </c>
       <c r="B131" t="n">
-        <v>79632</v>
+        <v>79629</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13625,32 +13625,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126600672</v>
+        <v>126600625</v>
       </c>
       <c r="B132" t="n">
-        <v>92615</v>
+        <v>78770</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13660,10 +13660,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>406273</v>
+        <v>406434</v>
       </c>
       <c r="R132" t="n">
-        <v>6856005</v>
+        <v>6856017</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13725,7 +13725,7 @@
         <v>126600638</v>
       </c>
       <c r="B133" t="n">
-        <v>78772</v>
+        <v>78769</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13822,7 +13822,7 @@
         <v>126600566</v>
       </c>
       <c r="B134" t="n">
-        <v>79632</v>
+        <v>79629</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13919,7 +13919,7 @@
         <v>126600536</v>
       </c>
       <c r="B135" t="n">
-        <v>79632</v>
+        <v>79629</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14016,7 +14016,7 @@
         <v>126600676</v>
       </c>
       <c r="B136" t="n">
-        <v>92615</v>
+        <v>92609</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14207,32 +14207,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126600633</v>
+        <v>126600607</v>
       </c>
       <c r="B138" t="n">
-        <v>78772</v>
+        <v>97314</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6446</v>
+        <v>221945</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14242,10 +14242,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>406528</v>
+        <v>406576</v>
       </c>
       <c r="R138" t="n">
-        <v>6855666</v>
+        <v>6856013</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14304,10 +14304,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126600540</v>
+        <v>126600633</v>
       </c>
       <c r="B139" t="n">
-        <v>79632</v>
+        <v>78769</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14315,21 +14315,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14339,10 +14339,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>406582</v>
+        <v>406528</v>
       </c>
       <c r="R139" t="n">
-        <v>6855833</v>
+        <v>6855666</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14401,10 +14401,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126600641</v>
+        <v>126600540</v>
       </c>
       <c r="B140" t="n">
-        <v>78772</v>
+        <v>79629</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14412,21 +14412,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14436,10 +14436,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>406491</v>
+        <v>406582</v>
       </c>
       <c r="R140" t="n">
-        <v>6855856</v>
+        <v>6855833</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14498,10 +14498,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126600547</v>
+        <v>126600641</v>
       </c>
       <c r="B141" t="n">
-        <v>79632</v>
+        <v>78769</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14509,21 +14509,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14533,10 +14533,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>406285</v>
+        <v>406491</v>
       </c>
       <c r="R141" t="n">
-        <v>6856129</v>
+        <v>6855856</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14595,32 +14595,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126600607</v>
+        <v>126600667</v>
       </c>
       <c r="B142" t="n">
-        <v>97320</v>
+        <v>79011</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14630,10 +14630,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>406576</v>
+        <v>406426</v>
       </c>
       <c r="R142" t="n">
-        <v>6856013</v>
+        <v>6855972</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14692,10 +14692,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>126600667</v>
+        <v>126600547</v>
       </c>
       <c r="B143" t="n">
-        <v>79014</v>
+        <v>79629</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14703,21 +14703,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14727,10 +14727,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>406426</v>
+        <v>406285</v>
       </c>
       <c r="R143" t="n">
-        <v>6855972</v>
+        <v>6856129</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>

--- a/artfynd/A 29779-2025 artfynd.xlsx
+++ b/artfynd/A 29779-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY144"/>
+  <dimension ref="A1:AZ144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600678</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600679</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600680</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600681</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600682</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600631</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600611</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600586</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1550,6 +1595,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606872</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1652,6 +1702,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606875</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1754,6 +1809,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610430</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1856,6 +1916,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610433</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1958,6 +2023,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610435</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2064,6 +2134,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126017344</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2161,6 +2236,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600672</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2258,6 +2338,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600673</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2355,6 +2440,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600675</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2452,6 +2542,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600676</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2549,6 +2644,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600677</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2651,6 +2751,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606873</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2753,6 +2858,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606874</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2855,6 +2965,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610431</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2957,6 +3072,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610432</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3059,6 +3179,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610434</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3161,6 +3286,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610436</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3258,6 +3388,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600591</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3360,6 +3495,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600652</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3457,6 +3597,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600653</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3554,6 +3699,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600654</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3651,6 +3801,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600655</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3748,6 +3903,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600656</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3845,6 +4005,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600657</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3942,6 +4107,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600658</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4039,6 +4209,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600659</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4136,6 +4311,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600660</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4233,6 +4413,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600663</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4330,6 +4515,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600664</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4427,6 +4617,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600665</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4524,6 +4719,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600666</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4621,6 +4821,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600667</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4718,6 +4923,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600668</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4815,6 +5025,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600669</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4912,6 +5127,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600683</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5009,6 +5229,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600684</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5106,6 +5331,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600688</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5203,6 +5433,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600587</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5309,6 +5544,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124825273</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5406,6 +5646,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600632</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5503,6 +5748,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600633</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5600,6 +5850,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600634</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5697,6 +5952,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600635</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5794,6 +6054,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600636</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5891,6 +6156,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600637</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5988,6 +6258,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600638</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6085,6 +6360,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600639</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6182,6 +6462,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600640</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6279,6 +6564,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600641</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6376,6 +6666,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600642</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6473,6 +6768,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600643</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6570,6 +6870,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600644</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6667,6 +6972,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600645</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6764,6 +7074,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600535</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6861,6 +7176,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600536</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6958,6 +7278,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600537</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7055,6 +7380,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600538</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7152,6 +7482,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600539</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7249,6 +7584,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600540</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7346,6 +7686,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600541</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7443,6 +7788,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600542</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7540,6 +7890,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600543</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7637,6 +7992,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600544</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7734,6 +8094,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600545</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7831,6 +8196,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600546</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7928,6 +8298,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600547</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8025,6 +8400,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600548</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8122,6 +8502,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600549</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8219,6 +8604,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600551</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8316,6 +8706,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600552</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8413,6 +8808,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600553</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8510,6 +8910,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600554</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8607,6 +9012,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600555</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8704,6 +9114,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600556</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8801,6 +9216,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600557</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8898,6 +9318,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600558</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -8995,6 +9420,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600559</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9092,6 +9522,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600560</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9189,6 +9624,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600561</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9286,6 +9726,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600562</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9383,6 +9828,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600563</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9480,6 +9930,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600564</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9577,6 +10032,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600565</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9674,6 +10134,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600566</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9771,6 +10236,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600567</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9868,6 +10338,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600568</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -9965,6 +10440,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600569</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10062,6 +10542,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600570</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10159,6 +10644,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600571</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10256,6 +10746,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600572</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10353,6 +10848,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600573</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10450,6 +10950,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600574</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10547,6 +11052,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600575</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10644,6 +11154,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600576</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10741,6 +11256,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600577</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -10838,6 +11358,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600578</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -10935,6 +11460,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600579</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11032,6 +11562,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600580</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11129,6 +11664,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600581</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11226,6 +11766,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600582</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11323,6 +11868,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600584</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11420,6 +11970,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600585</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11517,6 +12072,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600685</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11624,6 +12184,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600605</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -11725,6 +12290,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600593</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -11822,6 +12392,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600594</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -11919,6 +12494,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600595</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12016,6 +12596,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600596</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12118,6 +12703,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600534</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12224,6 +12814,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124825272</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12330,6 +12925,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126017342</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12427,6 +13027,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600608</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12524,6 +13129,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600606</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -12621,6 +13231,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600607</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -12718,6 +13333,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600601</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -12820,6 +13440,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600613</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -12917,6 +13542,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600614</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13014,6 +13644,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600615</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13111,6 +13746,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600616</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13208,6 +13848,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600617</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13305,6 +13950,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600618</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13402,6 +14052,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600619</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -13499,6 +14154,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600620</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -13596,6 +14256,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600621</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -13693,6 +14358,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600622</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -13790,6 +14460,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600623</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -13887,6 +14562,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600624</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -13984,6 +14664,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600625</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14081,6 +14766,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600626</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14178,6 +14868,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600627</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14275,6 +14970,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600628</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -14372,6 +15072,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600629</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -14469,6 +15174,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600630</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -14566,6 +15276,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600589</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -14663,8 +15378,158 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600590</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>